--- a/news_daily/2026-09-18.xlsx
+++ b/news_daily/2026-09-18.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH41"/>
+  <dimension ref="A1:BL41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -999,6 +1023,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1169,6 +1197,10 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1339,6 +1371,10 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1509,6 +1545,10 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1671,6 +1711,10 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1841,6 +1885,10 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2011,6 +2059,10 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2181,6 +2233,10 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2351,6 +2407,10 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2521,6 +2581,10 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr"/>
+      <c r="BL11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2691,6 +2755,10 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2861,6 +2929,10 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3031,168 +3103,200 @@
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr"/>
+      <c r="BL14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Amazon Prime settlement expands: More consumers eligible for refunds up to $200</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>0.899</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNRGM0WWxUbERMdnNUYVMzbDB0R1JsUHpGMk5Lc3V5UjBFTjRyVm1fajNReWNpcXNRc25xUVMwUzN3aXpYbmlWZmtMLWRtNlNMTE9ET1ZNRFhheTdMMXBfRk5ZTEF0OFplaGZOUk82XzNQY0Q1eVpIQl93UHhGbUVSMU1aMEM2Zkw4ajI5YWRVWmxsaFQtdm1SajhnNi1rWTZyNTFzRWN6aDNzaVUxQllLSTN5TUtYdFlfUUN4eDFrWFV6QW8?oc=5</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>News4JAX</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>78932fda4a45479c869e42d3a7b1ebcf</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>0fc24e64eb0939a1d337b0fe</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr">
+        <is>
+          <t>edd52ac9baec10ec5afba764</t>
+        </is>
+      </c>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>0.899</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNRGM0WWxUbERMdnNUYVMzbDB0R1JsUHpGMk5Lc3V5UjBFTjRyVm1fajNReWNpcXNRc25xUVMwUzN3aXpYbmlWZmtMLWRtNlNMTE9ET1ZNRFhheTdMMXBfRk5ZTEF0OFplaGZOUk82XzNQY0Q1eVpIQl93UHhGbUVSMU1aMEM2Zkw4ajI5YWRVWmxsaFQtdm1SajhnNi1rWTZyNTFzRWN6aDNzaVUxQllLSTN5TUtYdFlfUUN4eDFrWFV6QW8?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>News4JAX</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>0fc24e64eb0939a1d337b0fe</t>
-        </is>
-      </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>edd52ac9baec10ec5afba764</t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr"/>
-      <c r="AF15" s="4" t="inlineStr"/>
-      <c r="AG15" s="4" t="inlineStr"/>
-      <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="inlineStr"/>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr"/>
-      <c r="AL15" s="4" t="inlineStr"/>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr"/>
-      <c r="AP15" s="4" t="inlineStr"/>
-      <c r="AQ15" s="4" t="inlineStr"/>
-      <c r="AR15" s="4" t="inlineStr"/>
-      <c r="AS15" s="4" t="inlineStr"/>
-      <c r="AT15" s="4" t="inlineStr"/>
-      <c r="AU15" s="4" t="inlineStr"/>
-      <c r="AV15" s="4" t="inlineStr"/>
-      <c r="AW15" s="4" t="inlineStr"/>
-      <c r="AX15" s="4" t="inlineStr"/>
-      <c r="AY15" s="4" t="inlineStr"/>
-      <c r="AZ15" s="4" t="inlineStr"/>
-      <c r="BA15" s="4" t="inlineStr"/>
-      <c r="BB15" s="4" t="inlineStr">
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr"/>
+      <c r="AS15" s="3" t="inlineStr"/>
+      <c r="AT15" s="3" t="inlineStr"/>
+      <c r="AU15" s="3" t="inlineStr"/>
+      <c r="AV15" s="3" t="inlineStr"/>
+      <c r="AW15" s="3" t="inlineStr"/>
+      <c r="AX15" s="3" t="inlineStr"/>
+      <c r="AY15" s="3" t="inlineStr"/>
+      <c r="AZ15" s="3" t="inlineStr"/>
+      <c r="BA15" s="3" t="inlineStr"/>
+      <c r="BB15" s="3" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="BC15" s="4" t="inlineStr">
+      <c r="BC15" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="4" t="inlineStr"/>
-      <c r="BE15" s="4" t="inlineStr">
+      <c r="BD15" s="3" t="inlineStr"/>
+      <c r="BE15" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF15" s="4" t="inlineStr"/>
-      <c r="BG15" s="4" t="inlineStr">
+      <c r="BF15" s="3" t="inlineStr"/>
+      <c r="BG15" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH15" s="4" t="inlineStr"/>
+      <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3363,6 +3467,10 @@
         </is>
       </c>
       <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr"/>
+      <c r="BL16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3533,6 +3641,10 @@
         </is>
       </c>
       <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BI17" s="3" t="inlineStr"/>
+      <c r="BJ17" s="3" t="inlineStr"/>
+      <c r="BK17" s="3" t="inlineStr"/>
+      <c r="BL17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3695,6 +3807,10 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3865,6 +3981,10 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4027,168 +4147,200 @@
         </is>
       </c>
       <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BJ20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr"/>
+      <c r="BL20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Amazon FTC settlement update: More Prime members qualify and payout increased to $200</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>0.933</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPWm10V285QU4ydXZZTHhxcFg2bENfdTFIYzFrbjhRSWRpd0VVVnZHUERTTkNUb2lSQXJ1eDJzSi13RXNPeEg2MFZzR3Fwb3JZMC1zMWZoSkRXUkx2SXlyMDE1dHV3QmlVbmd5a1JiUy1VUldOZTlKRXg0akE1aDNRVUM0cG9HMEQ5Q3B0Umozc3M3NWVQdjYxRUNEdmxmbmI2WWI4d29TOHgzajRIbFllUE50RlNYVW84Ym51WmM4RmFPdGpHbGVXVFY0M29lbVF2Mm1mMGp1ONIB3wFBVV95cUxNY3M5Z01EbDR1UHdGWEpET3Q1eWgtZllNUkhQNXBUNkRkUFp6RlFkNWdmaXNsRGFNcHJNOHJuQ2ZzMzI5dXR5bTVncGhPd3BCX3ZkZ2EyRzNrTDJsTW9pRjFKWlNQQzNDLUNTaW94a2NGU0hZbHRTeVFjVlliOGt3dWRzN2VleEFhYnFSV2Z4azlOdEFGZWdWQTkzVUxPUmdYS1E1aFhTcXZkUXlOYWlsOHdkMHlwdUxnUWwyQlhVdW94TXRXTzJ3amwxZkY1ZGpCMkNDaDVFZ0VWcXd3WFVN?oc=5</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>NBC Connecticut</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr"/>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>a95dc82d9c8041f89695449889ffa114</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>19458ffd5127974021f4396b</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>e01a8a51d5d5baea7830f612</t>
+        </is>
+      </c>
+      <c r="AE21" s="3" t="inlineStr"/>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr"/>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+      <c r="AM21" s="3" t="inlineStr"/>
+      <c r="AN21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>0.933</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPWm10V285QU4ydXZZTHhxcFg2bENfdTFIYzFrbjhRSWRpd0VVVnZHUERTTkNUb2lSQXJ1eDJzSi13RXNPeEg2MFZzR3Fwb3JZMC1zMWZoSkRXUkx2SXlyMDE1dHV3QmlVbmd5a1JiUy1VUldOZTlKRXg0akE1aDNRVUM0cG9HMEQ5Q3B0Umozc3M3NWVQdjYxRUNEdmxmbmI2WWI4d29TOHgzajRIbFllUE50RlNYVW84Ym51WmM4RmFPdGpHbGVXVFY0M29lbVF2Mm1mMGp1ONIB3wFBVV95cUxNY3M5Z01EbDR1UHdGWEpET3Q1eWgtZllNUkhQNXBUNkRkUFp6RlFkNWdmaXNsRGFNcHJNOHJuQ2ZzMzI5dXR5bTVncGhPd3BCX3ZkZ2EyRzNrTDJsTW9pRjFKWlNQQzNDLUNTaW94a2NGU0hZbHRTeVFjVlliOGt3dWRzN2VleEFhYnFSV2Z4azlOdEFGZWdWQTkzVUxPUmdYS1E1aFhTcXZkUXlOYWlsOHdkMHlwdUxnUWwyQlhVdW94TXRXTzJ3amwxZkY1ZGpCMkNDaDVFZ0VWcXd3WFVN?oc=5</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>NBC Connecticut</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y21" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z21" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="inlineStr">
-        <is>
-          <t>19458ffd5127974021f4396b</t>
-        </is>
-      </c>
-      <c r="AD21" s="4" t="inlineStr">
-        <is>
-          <t>e01a8a51d5d5baea7830f612</t>
-        </is>
-      </c>
-      <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="inlineStr"/>
-      <c r="AG21" s="4" t="inlineStr"/>
-      <c r="AH21" s="4" t="inlineStr"/>
-      <c r="AI21" s="4" t="inlineStr"/>
-      <c r="AJ21" s="4" t="inlineStr"/>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="inlineStr"/>
-      <c r="AM21" s="4" t="inlineStr"/>
-      <c r="AN21" s="4" t="inlineStr"/>
-      <c r="AO21" s="4" t="inlineStr"/>
-      <c r="AP21" s="4" t="inlineStr"/>
-      <c r="AQ21" s="4" t="inlineStr"/>
-      <c r="AR21" s="4" t="inlineStr"/>
-      <c r="AS21" s="4" t="inlineStr"/>
-      <c r="AT21" s="4" t="inlineStr"/>
-      <c r="AU21" s="4" t="inlineStr"/>
-      <c r="AV21" s="4" t="inlineStr"/>
-      <c r="AW21" s="4" t="inlineStr"/>
-      <c r="AX21" s="4" t="inlineStr"/>
-      <c r="AY21" s="4" t="inlineStr"/>
-      <c r="AZ21" s="4" t="inlineStr"/>
-      <c r="BA21" s="4" t="inlineStr"/>
-      <c r="BB21" s="4" t="inlineStr">
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr"/>
+      <c r="AS21" s="3" t="inlineStr"/>
+      <c r="AT21" s="3" t="inlineStr"/>
+      <c r="AU21" s="3" t="inlineStr"/>
+      <c r="AV21" s="3" t="inlineStr"/>
+      <c r="AW21" s="3" t="inlineStr"/>
+      <c r="AX21" s="3" t="inlineStr"/>
+      <c r="AY21" s="3" t="inlineStr"/>
+      <c r="AZ21" s="3" t="inlineStr"/>
+      <c r="BA21" s="3" t="inlineStr"/>
+      <c r="BB21" s="3" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="BC21" s="4" t="inlineStr">
+      <c r="BC21" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD21" s="4" t="inlineStr"/>
-      <c r="BE21" s="4" t="inlineStr">
+      <c r="BD21" s="3" t="inlineStr"/>
+      <c r="BE21" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF21" s="4" t="inlineStr"/>
-      <c r="BG21" s="4" t="inlineStr">
+      <c r="BF21" s="3" t="inlineStr"/>
+      <c r="BG21" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH21" s="4" t="inlineStr"/>
+      <c r="BH21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -4229,7 +4381,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -4239,13 +4391,17 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -4285,7 +4441,7 @@
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
@@ -4294,7 +4450,11 @@
         </is>
       </c>
       <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="inlineStr"/>
+      <c r="AB22" s="4" t="inlineStr">
+        <is>
+          <t>feb485e895ff479fa1c582b674c6692b</t>
+        </is>
+      </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
           <t>3510532871d2cfa2d2ebe2db</t>
@@ -4315,7 +4475,11 @@
       <c r="AL22" s="4" t="inlineStr"/>
       <c r="AM22" s="4" t="inlineStr"/>
       <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="inlineStr"/>
+      <c r="AO22" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="4" t="inlineStr"/>
       <c r="AQ22" s="4" t="inlineStr"/>
       <c r="AR22" s="4" t="inlineStr"/>
@@ -4359,6 +4523,22 @@
         </is>
       </c>
       <c r="BH22" s="4" t="inlineStr"/>
+      <c r="BI22" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ22" s="4" t="inlineStr"/>
+      <c r="BK22" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -4395,7 +4575,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -4405,17 +4585,17 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -4455,7 +4635,7 @@
       </c>
       <c r="Y23" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z23" s="4" t="inlineStr">
@@ -4464,7 +4644,11 @@
         </is>
       </c>
       <c r="AA23" s="4" t="inlineStr"/>
-      <c r="AB23" s="4" t="inlineStr"/>
+      <c r="AB23" s="4" t="inlineStr">
+        <is>
+          <t>f9c2c41e84d44272a0f0c95ac8d183a6</t>
+        </is>
+      </c>
       <c r="AC23" s="4" t="inlineStr">
         <is>
           <t>ae25e2a980721ffff21bb447</t>
@@ -4487,7 +4671,7 @@
       <c r="AN23" s="4" t="inlineStr"/>
       <c r="AO23" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP23" s="4" t="inlineStr"/>
@@ -4529,176 +4713,220 @@
       </c>
       <c r="BG23" s="4" t="inlineStr"/>
       <c r="BH23" s="4" t="inlineStr"/>
+      <c r="BI23" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ23" s="4" t="inlineStr"/>
+      <c r="BK23" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>ELV</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Elevance Health, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Elevance Health sued again over out-of-network penalty</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>'-0.921</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQS1pxV1FvM3FTdlRxVnhJSmVjZlY0RXFMQ2FqV21sczQ3TDJjZ1FqYU9kdGJLMHgxVTVhd0dYZEdfbkNYNldGZ2t1N0UtUTB2QjhlUXk5S1V1cWFSM1BneHRNN3lBQ2NLOGUwcVZIVjVxd2RSaTlsbGoyM0ptWUNXT0hJZGlKdEVNRU0xUUlnUHQ3LTBfbG9NWkhpcUxLbWpCOEVz?oc=5</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>Modern Healthcare</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>penalty</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr"/>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>9e916820f92d4057a9a896412fa058af</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>5ef77219c82af0a31b781c5e</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr">
+        <is>
+          <t>6685c6a98dabcf0e53e4ec02</t>
+        </is>
+      </c>
+      <c r="AE24" s="3" t="inlineStr"/>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr"/>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="3" t="inlineStr"/>
+      <c r="AN24" s="3" t="inlineStr"/>
+      <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>'-0.921</t>
-        </is>
-      </c>
-      <c r="P24" s="4" t="inlineStr"/>
-      <c r="Q24" s="4" t="inlineStr"/>
-      <c r="R24" s="4" t="inlineStr"/>
-      <c r="S24" s="4" t="inlineStr"/>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQS1pxV1FvM3FTdlRxVnhJSmVjZlY0RXFMQ2FqV21sczQ3TDJjZ1FqYU9kdGJLMHgxVTVhd0dYZEdfbkNYNldGZ2t1N0UtUTB2QjhlUXk5S1V1cWFSM1BneHRNN3lBQ2NLOGUwcVZIVjVxd2RSaTlsbGoyM0ptWUNXT0hJZGlKdEVNRU0xUUlnUHQ3LTBfbG9NWkhpcUxLbWpCOEVz?oc=5</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>Modern Healthcare</t>
-        </is>
-      </c>
-      <c r="W24" s="4" t="inlineStr"/>
-      <c r="X24" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y24" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z24" s="4" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="AA24" s="4" t="inlineStr"/>
-      <c r="AB24" s="4" t="inlineStr"/>
-      <c r="AC24" s="4" t="inlineStr">
-        <is>
-          <t>5ef77219c82af0a31b781c5e</t>
-        </is>
-      </c>
-      <c r="AD24" s="4" t="inlineStr">
-        <is>
-          <t>6685c6a98dabcf0e53e4ec02</t>
-        </is>
-      </c>
-      <c r="AE24" s="4" t="inlineStr"/>
-      <c r="AF24" s="4" t="inlineStr"/>
-      <c r="AG24" s="4" t="inlineStr"/>
-      <c r="AH24" s="4" t="inlineStr"/>
-      <c r="AI24" s="4" t="inlineStr"/>
-      <c r="AJ24" s="4" t="inlineStr"/>
-      <c r="AK24" s="4" t="inlineStr"/>
-      <c r="AL24" s="4" t="inlineStr"/>
-      <c r="AM24" s="4" t="inlineStr"/>
-      <c r="AN24" s="4" t="inlineStr"/>
-      <c r="AO24" s="4" t="inlineStr"/>
-      <c r="AP24" s="4" t="inlineStr"/>
-      <c r="AQ24" s="4" t="inlineStr"/>
-      <c r="AR24" s="4" t="inlineStr"/>
-      <c r="AS24" s="4" t="inlineStr"/>
-      <c r="AT24" s="4" t="inlineStr"/>
-      <c r="AU24" s="4" t="inlineStr"/>
-      <c r="AV24" s="4" t="inlineStr"/>
-      <c r="AW24" s="4" t="inlineStr">
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr"/>
+      <c r="AS24" s="3" t="inlineStr"/>
+      <c r="AT24" s="3" t="inlineStr"/>
+      <c r="AU24" s="3" t="inlineStr"/>
+      <c r="AV24" s="3" t="inlineStr"/>
+      <c r="AW24" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX24" s="4" t="inlineStr"/>
-      <c r="AY24" s="4" t="inlineStr"/>
-      <c r="AZ24" s="4" t="inlineStr"/>
-      <c r="BA24" s="4" t="inlineStr"/>
-      <c r="BB24" s="4" t="inlineStr">
+      <c r="AX24" s="3" t="inlineStr"/>
+      <c r="AY24" s="3" t="inlineStr"/>
+      <c r="AZ24" s="3" t="inlineStr"/>
+      <c r="BA24" s="3" t="inlineStr"/>
+      <c r="BB24" s="3" t="inlineStr">
         <is>
           <t>ELV</t>
         </is>
       </c>
-      <c r="BC24" s="4" t="inlineStr">
+      <c r="BC24" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD24" s="4" t="inlineStr"/>
-      <c r="BE24" s="4" t="inlineStr">
+      <c r="BD24" s="3" t="inlineStr"/>
+      <c r="BE24" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF24" s="4" t="inlineStr">
+      <c r="BF24" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG24" s="4" t="inlineStr">
+      <c r="BG24" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH24" s="4" t="inlineStr"/>
+      <c r="BH24" s="3" t="inlineStr"/>
+      <c r="BI24" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ24" s="3" t="inlineStr"/>
+      <c r="BK24" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -4749,13 +4977,17 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -4804,7 +5036,11 @@
         </is>
       </c>
       <c r="AA25" s="4" t="inlineStr"/>
-      <c r="AB25" s="4" t="inlineStr"/>
+      <c r="AB25" s="4" t="inlineStr">
+        <is>
+          <t>080368e1826548a185195ca8fefea84a</t>
+        </is>
+      </c>
       <c r="AC25" s="4" t="inlineStr">
         <is>
           <t>bc328f72682b113464f72997</t>
@@ -4825,7 +5061,11 @@
       <c r="AL25" s="4" t="inlineStr"/>
       <c r="AM25" s="4" t="inlineStr"/>
       <c r="AN25" s="4" t="inlineStr"/>
-      <c r="AO25" s="4" t="inlineStr"/>
+      <c r="AO25" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP25" s="4" t="inlineStr"/>
       <c r="AQ25" s="4" t="inlineStr"/>
       <c r="AR25" s="4" t="inlineStr"/>
@@ -4861,6 +5101,18 @@
         </is>
       </c>
       <c r="BH25" s="4" t="inlineStr"/>
+      <c r="BI25" s="4" t="inlineStr"/>
+      <c r="BJ25" s="4" t="inlineStr"/>
+      <c r="BK25" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -4911,13 +5163,17 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -4966,7 +5222,11 @@
         </is>
       </c>
       <c r="AA26" s="4" t="inlineStr"/>
-      <c r="AB26" s="4" t="inlineStr"/>
+      <c r="AB26" s="4" t="inlineStr">
+        <is>
+          <t>adce91ba1d434f38a5baaf8245f1c011</t>
+        </is>
+      </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
           <t>083b3b5318369b358a750650</t>
@@ -4987,7 +5247,11 @@
       <c r="AL26" s="4" t="inlineStr"/>
       <c r="AM26" s="4" t="inlineStr"/>
       <c r="AN26" s="4" t="inlineStr"/>
-      <c r="AO26" s="4" t="inlineStr"/>
+      <c r="AO26" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP26" s="4" t="inlineStr"/>
       <c r="AQ26" s="4" t="inlineStr"/>
       <c r="AR26" s="4" t="inlineStr"/>
@@ -5031,346 +5295,414 @@
         </is>
       </c>
       <c r="BH26" s="4" t="inlineStr"/>
+      <c r="BI26" s="4" t="inlineStr"/>
+      <c r="BJ26" s="4" t="inlineStr"/>
+      <c r="BK26" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Mastercard Incorporated Common Stock</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Visa, Mastercard $167.5 million settlement could mean money for ATM users. Who qualifies.</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>'-0.486</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNVWtmbzlqT1pvM0k5bXJyMmJzSzZKNXU5bmNsSUoxNlZBSW9SOTlDTHdmUWZoMGo0ZEJleTEzTlgxWDg2VlBrMmJZTDJsQUktcVBEelRBTWs0cnNJeFJMWXlldWdJV3F5N0tUVzREY2hCRnd3OHJLZzJfS01CNEVlbkhBMC05R3RPdThqOWxoRXVJanBHWllvOUdvX041azJ0TzJIUjRnNXZkSUh2ZXpnM1pLSmtMTkRlSFJyMDZtaVFMUnp4dUUxVEpCN2RsU0ZDaHpnVVlvUEZEUDBFNkRXRXczM3lqMmFneUJadDRhbw?oc=5</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr"/>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>e4d4a7c19cba4c4cbae1ea8d37ae4d72</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>43b436b1305690f1d50e59b0</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr">
+        <is>
+          <t>0bda3f4d7ae943fc690ebc6a</t>
+        </is>
+      </c>
+      <c r="AE27" s="3" t="inlineStr"/>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr"/>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr"/>
+      <c r="AM27" s="3" t="inlineStr"/>
+      <c r="AN27" s="3" t="inlineStr"/>
+      <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>'-0.486</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr"/>
-      <c r="Q27" s="4" t="inlineStr"/>
-      <c r="R27" s="4" t="inlineStr"/>
-      <c r="S27" s="4" t="inlineStr"/>
-      <c r="T27" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNVWtmbzlqT1pvM0k5bXJyMmJzSzZKNXU5bmNsSUoxNlZBSW9SOTlDTHdmUWZoMGo0ZEJleTEzTlgxWDg2VlBrMmJZTDJsQUktcVBEelRBTWs0cnNJeFJMWXlldWdJV3F5N0tUVzREY2hCRnd3OHJLZzJfS01CNEVlbkhBMC05R3RPdThqOWxoRXVJanBHWllvOUdvX041azJ0TzJIUjRnNXZkSUh2ZXpnM1pLSmtMTkRlSFJyMDZtaVFMUnp4dUUxVEpCN2RsU0ZDaHpnVVlvUEZEUDBFNkRXRXczM3lqMmFneUJadDRhbw?oc=5</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W27" s="4" t="inlineStr"/>
-      <c r="X27" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y27" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z27" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="inlineStr"/>
-      <c r="AC27" s="4" t="inlineStr">
-        <is>
-          <t>43b436b1305690f1d50e59b0</t>
-        </is>
-      </c>
-      <c r="AD27" s="4" t="inlineStr">
-        <is>
-          <t>0bda3f4d7ae943fc690ebc6a</t>
-        </is>
-      </c>
-      <c r="AE27" s="4" t="inlineStr"/>
-      <c r="AF27" s="4" t="inlineStr"/>
-      <c r="AG27" s="4" t="inlineStr"/>
-      <c r="AH27" s="4" t="inlineStr"/>
-      <c r="AI27" s="4" t="inlineStr"/>
-      <c r="AJ27" s="4" t="inlineStr"/>
-      <c r="AK27" s="4" t="inlineStr"/>
-      <c r="AL27" s="4" t="inlineStr"/>
-      <c r="AM27" s="4" t="inlineStr"/>
-      <c r="AN27" s="4" t="inlineStr"/>
-      <c r="AO27" s="4" t="inlineStr"/>
-      <c r="AP27" s="4" t="inlineStr"/>
-      <c r="AQ27" s="4" t="inlineStr"/>
-      <c r="AR27" s="4" t="inlineStr"/>
-      <c r="AS27" s="4" t="inlineStr"/>
-      <c r="AT27" s="4" t="inlineStr"/>
-      <c r="AU27" s="4" t="inlineStr"/>
-      <c r="AV27" s="4" t="inlineStr"/>
-      <c r="AW27" s="4" t="inlineStr">
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr"/>
+      <c r="AS27" s="3" t="inlineStr"/>
+      <c r="AT27" s="3" t="inlineStr"/>
+      <c r="AU27" s="3" t="inlineStr"/>
+      <c r="AV27" s="3" t="inlineStr"/>
+      <c r="AW27" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX27" s="4" t="inlineStr"/>
-      <c r="AY27" s="4" t="inlineStr"/>
-      <c r="AZ27" s="4" t="inlineStr"/>
-      <c r="BA27" s="4" t="inlineStr"/>
-      <c r="BB27" s="4" t="inlineStr">
+      <c r="AX27" s="3" t="inlineStr"/>
+      <c r="AY27" s="3" t="inlineStr"/>
+      <c r="AZ27" s="3" t="inlineStr"/>
+      <c r="BA27" s="3" t="inlineStr"/>
+      <c r="BB27" s="3" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="BC27" s="4" t="inlineStr">
+      <c r="BC27" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD27" s="4" t="inlineStr"/>
-      <c r="BE27" s="4" t="inlineStr">
+      <c r="BD27" s="3" t="inlineStr"/>
+      <c r="BE27" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF27" s="4" t="inlineStr">
+      <c r="BF27" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG27" s="4" t="inlineStr">
+      <c r="BG27" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH27" s="4" t="inlineStr"/>
+      <c r="BH27" s="3" t="inlineStr"/>
+      <c r="BI27" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ27" s="3" t="inlineStr"/>
+      <c r="BK27" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>WMT</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Walmart Inc.</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>The Morning Risk Report: Senators Ask FTC to Probe Walmart and Amazon Over Bots’ ‘Made in America’ Data</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr"/>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>'-0.477</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPMGVVNVRSaldHUXlHOFNEZ0c4d0RFYnZnaGd2Y21id05GMk9Wb0E1OHJZTW42UHRITU9PR05yOHFuMG9fVl85UThtSkRwTFFWNjhBc0VVSnpzTG9VMnR2b2dvWlhTc1FjbnkzRFQ5aGRfQl95a0pOOTZ5dXBxWE9TNjF4TzZHbU4tVUN1QTVzRWZUM1BIQ0lsZXR4Wkd4WEhGMGdnNDlOUWtmNG41bXh6X1RlMmhHaHRxdXR4b195U2p0QlZESnBPMTFXS2JXMWQtRXp3ampVZEZ3WmF2MVpndDBIZ1ZGcGs?oc=5</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>5fa0996bd2f34fba81edbc7f81c9b793</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>8c4eb03572356403ee2a4859</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr">
+        <is>
+          <t>4d32c640b9c8873434fc9a9d</t>
+        </is>
+      </c>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>'-0.477</t>
-        </is>
-      </c>
-      <c r="P28" s="4" t="inlineStr"/>
-      <c r="Q28" s="4" t="inlineStr"/>
-      <c r="R28" s="4" t="inlineStr"/>
-      <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPMGVVNVRSaldHUXlHOFNEZ0c4d0RFYnZnaGd2Y21id05GMk9Wb0E1OHJZTW42UHRITU9PR05yOHFuMG9fVl85UThtSkRwTFFWNjhBc0VVSnpzTG9VMnR2b2dvWlhTc1FjbnkzRFQ5aGRfQl95a0pOOTZ5dXBxWE9TNjF4TzZHbU4tVUN1QTVzRWZUM1BIQ0lsZXR4Wkd4WEhGMGdnNDlOUWtmNG41bXh6X1RlMmhHaHRxdXR4b195U2p0QlZESnBPMTFXS2JXMWQtRXp3ampVZEZ3WmF2MVpndDBIZ1ZGcGs?oc=5</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>WSJ</t>
-        </is>
-      </c>
-      <c r="W28" s="4" t="inlineStr"/>
-      <c r="X28" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y28" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z28" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA28" s="4" t="inlineStr"/>
-      <c r="AB28" s="4" t="inlineStr"/>
-      <c r="AC28" s="4" t="inlineStr">
-        <is>
-          <t>8c4eb03572356403ee2a4859</t>
-        </is>
-      </c>
-      <c r="AD28" s="4" t="inlineStr">
-        <is>
-          <t>4d32c640b9c8873434fc9a9d</t>
-        </is>
-      </c>
-      <c r="AE28" s="4" t="inlineStr"/>
-      <c r="AF28" s="4" t="inlineStr"/>
-      <c r="AG28" s="4" t="inlineStr"/>
-      <c r="AH28" s="4" t="inlineStr"/>
-      <c r="AI28" s="4" t="inlineStr"/>
-      <c r="AJ28" s="4" t="inlineStr"/>
-      <c r="AK28" s="4" t="inlineStr"/>
-      <c r="AL28" s="4" t="inlineStr"/>
-      <c r="AM28" s="4" t="inlineStr"/>
-      <c r="AN28" s="4" t="inlineStr"/>
-      <c r="AO28" s="4" t="inlineStr"/>
-      <c r="AP28" s="4" t="inlineStr"/>
-      <c r="AQ28" s="4" t="inlineStr"/>
-      <c r="AR28" s="4" t="inlineStr"/>
-      <c r="AS28" s="4" t="inlineStr"/>
-      <c r="AT28" s="4" t="inlineStr"/>
-      <c r="AU28" s="4" t="inlineStr"/>
-      <c r="AV28" s="4" t="inlineStr"/>
-      <c r="AW28" s="4" t="inlineStr">
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr"/>
+      <c r="AS28" s="3" t="inlineStr"/>
+      <c r="AT28" s="3" t="inlineStr"/>
+      <c r="AU28" s="3" t="inlineStr"/>
+      <c r="AV28" s="3" t="inlineStr"/>
+      <c r="AW28" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX28" s="4" t="inlineStr"/>
-      <c r="AY28" s="4" t="inlineStr"/>
-      <c r="AZ28" s="4" t="inlineStr"/>
-      <c r="BA28" s="4" t="inlineStr"/>
-      <c r="BB28" s="4" t="inlineStr">
+      <c r="AX28" s="3" t="inlineStr"/>
+      <c r="AY28" s="3" t="inlineStr"/>
+      <c r="AZ28" s="3" t="inlineStr"/>
+      <c r="BA28" s="3" t="inlineStr"/>
+      <c r="BB28" s="3" t="inlineStr">
         <is>
           <t>WMT</t>
         </is>
       </c>
-      <c r="BC28" s="4" t="inlineStr">
+      <c r="BC28" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD28" s="4" t="inlineStr"/>
-      <c r="BE28" s="4" t="inlineStr">
+      <c r="BD28" s="3" t="inlineStr"/>
+      <c r="BE28" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF28" s="4" t="inlineStr">
+      <c r="BF28" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG28" s="4" t="inlineStr">
+      <c r="BG28" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH28" s="4" t="inlineStr"/>
+      <c r="BH28" s="3" t="inlineStr"/>
+      <c r="BI28" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ28" s="3" t="inlineStr"/>
+      <c r="BK28" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -5421,13 +5753,17 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -5476,7 +5812,11 @@
         </is>
       </c>
       <c r="AA29" s="4" t="inlineStr"/>
-      <c r="AB29" s="4" t="inlineStr"/>
+      <c r="AB29" s="4" t="inlineStr">
+        <is>
+          <t>32fad879074b4e279a17274ae73b62c8</t>
+        </is>
+      </c>
       <c r="AC29" s="4" t="inlineStr">
         <is>
           <t>d72536a7bbcfac4b030ef4df</t>
@@ -5497,7 +5837,11 @@
       <c r="AL29" s="4" t="inlineStr"/>
       <c r="AM29" s="4" t="inlineStr"/>
       <c r="AN29" s="4" t="inlineStr"/>
-      <c r="AO29" s="4" t="inlineStr"/>
+      <c r="AO29" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP29" s="4" t="inlineStr"/>
       <c r="AQ29" s="4" t="inlineStr"/>
       <c r="AR29" s="4" t="inlineStr"/>
@@ -5541,6 +5885,18 @@
         </is>
       </c>
       <c r="BH29" s="4" t="inlineStr"/>
+      <c r="BI29" s="4" t="inlineStr"/>
+      <c r="BJ29" s="4" t="inlineStr"/>
+      <c r="BK29" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -5553,7 +5909,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>CPAY</t>
+        </is>
+      </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Corpay</t>
@@ -5577,7 +5937,7 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -5587,17 +5947,17 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -5637,7 +5997,7 @@
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z30" s="4" t="inlineStr">
@@ -5646,7 +6006,11 @@
         </is>
       </c>
       <c r="AA30" s="4" t="inlineStr"/>
-      <c r="AB30" s="4" t="inlineStr"/>
+      <c r="AB30" s="4" t="inlineStr">
+        <is>
+          <t>a567ea6c2e324a5a93f8179b2d7f5220</t>
+        </is>
+      </c>
       <c r="AC30" s="4" t="inlineStr">
         <is>
           <t>c35e8f22bda649ec16865913</t>
@@ -5669,7 +6033,7 @@
       <c r="AN30" s="4" t="inlineStr"/>
       <c r="AO30" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP30" s="4" t="inlineStr"/>
@@ -5711,662 +6075,790 @@
       </c>
       <c r="BG30" s="4" t="inlineStr"/>
       <c r="BH30" s="4" t="inlineStr"/>
+      <c r="BI30" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|Ticker|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ30" s="4" t="inlineStr"/>
+      <c r="BK30" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Amazon Prime customers could receive up to $200 in refunds under expanded FTC settlement</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr"/>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>0.057</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE4wblJEQzB3cXV4NmZuc0w4bmstRzFJcXYtSmNJVGVYRXptUklRUWExeDB3UUpGTDZPMWV2THZtTVdIWDhBZUxYalVLOGlUM3dKeXBpbzVMVWNCWkhRN1ZGNHV5SGl4alBUTnVpNEthTGVLZm9kb1Y4?oc=5</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>MyNorthwest.com</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr"/>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr"/>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>650480ef8a564785847a330af0e7eaee</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>d399e06478c17d4b082ba900</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr">
+        <is>
+          <t>95ebe81054411e953092304e</t>
+        </is>
+      </c>
+      <c r="AE31" s="3" t="inlineStr"/>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr"/>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr"/>
+      <c r="AM31" s="3" t="inlineStr"/>
+      <c r="AN31" s="3" t="inlineStr"/>
+      <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O31" s="4" t="inlineStr">
-        <is>
-          <t>0.057</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr"/>
-      <c r="Q31" s="4" t="inlineStr"/>
-      <c r="R31" s="4" t="inlineStr"/>
-      <c r="S31" s="4" t="inlineStr"/>
-      <c r="T31" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U31" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE4wblJEQzB3cXV4NmZuc0w4bmstRzFJcXYtSmNJVGVYRXptUklRUWExeDB3UUpGTDZPMWV2THZtTVdIWDhBZUxYalVLOGlUM3dKeXBpbzVMVWNCWkhRN1ZGNHV5SGl4alBUTnVpNEthTGVLZm9kb1Y4?oc=5</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="inlineStr">
-        <is>
-          <t>MyNorthwest.com</t>
-        </is>
-      </c>
-      <c r="W31" s="4" t="inlineStr"/>
-      <c r="X31" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y31" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z31" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA31" s="4" t="inlineStr"/>
-      <c r="AB31" s="4" t="inlineStr"/>
-      <c r="AC31" s="4" t="inlineStr">
-        <is>
-          <t>d399e06478c17d4b082ba900</t>
-        </is>
-      </c>
-      <c r="AD31" s="4" t="inlineStr">
-        <is>
-          <t>95ebe81054411e953092304e</t>
-        </is>
-      </c>
-      <c r="AE31" s="4" t="inlineStr"/>
-      <c r="AF31" s="4" t="inlineStr"/>
-      <c r="AG31" s="4" t="inlineStr"/>
-      <c r="AH31" s="4" t="inlineStr"/>
-      <c r="AI31" s="4" t="inlineStr"/>
-      <c r="AJ31" s="4" t="inlineStr"/>
-      <c r="AK31" s="4" t="inlineStr"/>
-      <c r="AL31" s="4" t="inlineStr"/>
-      <c r="AM31" s="4" t="inlineStr"/>
-      <c r="AN31" s="4" t="inlineStr"/>
-      <c r="AO31" s="4" t="inlineStr"/>
-      <c r="AP31" s="4" t="inlineStr"/>
-      <c r="AQ31" s="4" t="inlineStr"/>
-      <c r="AR31" s="4" t="inlineStr"/>
-      <c r="AS31" s="4" t="inlineStr"/>
-      <c r="AT31" s="4" t="inlineStr"/>
-      <c r="AU31" s="4" t="inlineStr"/>
-      <c r="AV31" s="4" t="inlineStr"/>
-      <c r="AW31" s="4" t="inlineStr"/>
-      <c r="AX31" s="4" t="inlineStr"/>
-      <c r="AY31" s="4" t="inlineStr"/>
-      <c r="AZ31" s="4" t="inlineStr"/>
-      <c r="BA31" s="4" t="inlineStr"/>
-      <c r="BB31" s="4" t="inlineStr">
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr"/>
+      <c r="AS31" s="3" t="inlineStr"/>
+      <c r="AT31" s="3" t="inlineStr"/>
+      <c r="AU31" s="3" t="inlineStr"/>
+      <c r="AV31" s="3" t="inlineStr"/>
+      <c r="AW31" s="3" t="inlineStr"/>
+      <c r="AX31" s="3" t="inlineStr"/>
+      <c r="AY31" s="3" t="inlineStr"/>
+      <c r="AZ31" s="3" t="inlineStr"/>
+      <c r="BA31" s="3" t="inlineStr"/>
+      <c r="BB31" s="3" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="BC31" s="4" t="inlineStr">
+      <c r="BC31" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD31" s="4" t="inlineStr"/>
-      <c r="BE31" s="4" t="inlineStr">
+      <c r="BD31" s="3" t="inlineStr"/>
+      <c r="BE31" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF31" s="4" t="inlineStr"/>
-      <c r="BG31" s="4" t="inlineStr">
+      <c r="BF31" s="3" t="inlineStr"/>
+      <c r="BG31" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH31" s="4" t="inlineStr"/>
+      <c r="BH31" s="3" t="inlineStr"/>
+      <c r="BI31" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ31" s="3" t="inlineStr"/>
+      <c r="BK31" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Amazon Prime customers may be eligible to receive $200 as settlement grows</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr"/>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPTF9jaHpTRUh6QjlHbm5aMVJfa2pCQVdYTlFINmd1U0pQVzlRSnBNNmdEYmFBMjBQVHFwZ0hhSGxXalNhTHFaU29WTGJjYnJSYVU0dGl3ZnVVSmQ0YkZMN05UY3A2VDZHbkxPc2lKX29aYThKeTJWYWFGX3hZRnYwa0tHMFoycHRRbEt4XzJSdWJObGo1d1ZyaW83RFk?oc=5</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>Dallas News</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr"/>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>befdb98e6d5543598da4f2fb71ea8909</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>cf3548bf28669271ba85d455</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr">
+        <is>
+          <t>610a60c13836ba4e753cc26d</t>
+        </is>
+      </c>
+      <c r="AE32" s="3" t="inlineStr"/>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr"/>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr"/>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr"/>
+      <c r="AM32" s="3" t="inlineStr"/>
+      <c r="AN32" s="3" t="inlineStr"/>
+      <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="inlineStr"/>
-      <c r="Q32" s="4" t="inlineStr"/>
-      <c r="R32" s="4" t="inlineStr"/>
-      <c r="S32" s="4" t="inlineStr"/>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPTF9jaHpTRUh6QjlHbm5aMVJfa2pCQVdYTlFINmd1U0pQVzlRSnBNNmdEYmFBMjBQVHFwZ0hhSGxXalNhTHFaU29WTGJjYnJSYVU0dGl3ZnVVSmQ0YkZMN05UY3A2VDZHbkxPc2lKX29aYThKeTJWYWFGX3hZRnYwa0tHMFoycHRRbEt4XzJSdWJObGo1d1ZyaW83RFk?oc=5</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>Dallas News</t>
-        </is>
-      </c>
-      <c r="W32" s="4" t="inlineStr"/>
-      <c r="X32" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y32" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z32" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA32" s="4" t="inlineStr"/>
-      <c r="AB32" s="4" t="inlineStr"/>
-      <c r="AC32" s="4" t="inlineStr">
-        <is>
-          <t>cf3548bf28669271ba85d455</t>
-        </is>
-      </c>
-      <c r="AD32" s="4" t="inlineStr">
-        <is>
-          <t>610a60c13836ba4e753cc26d</t>
-        </is>
-      </c>
-      <c r="AE32" s="4" t="inlineStr"/>
-      <c r="AF32" s="4" t="inlineStr"/>
-      <c r="AG32" s="4" t="inlineStr"/>
-      <c r="AH32" s="4" t="inlineStr"/>
-      <c r="AI32" s="4" t="inlineStr"/>
-      <c r="AJ32" s="4" t="inlineStr"/>
-      <c r="AK32" s="4" t="inlineStr"/>
-      <c r="AL32" s="4" t="inlineStr"/>
-      <c r="AM32" s="4" t="inlineStr"/>
-      <c r="AN32" s="4" t="inlineStr"/>
-      <c r="AO32" s="4" t="inlineStr"/>
-      <c r="AP32" s="4" t="inlineStr"/>
-      <c r="AQ32" s="4" t="inlineStr"/>
-      <c r="AR32" s="4" t="inlineStr"/>
-      <c r="AS32" s="4" t="inlineStr"/>
-      <c r="AT32" s="4" t="inlineStr"/>
-      <c r="AU32" s="4" t="inlineStr"/>
-      <c r="AV32" s="4" t="inlineStr"/>
-      <c r="AW32" s="4" t="inlineStr"/>
-      <c r="AX32" s="4" t="inlineStr"/>
-      <c r="AY32" s="4" t="inlineStr"/>
-      <c r="AZ32" s="4" t="inlineStr"/>
-      <c r="BA32" s="4" t="inlineStr"/>
-      <c r="BB32" s="4" t="inlineStr">
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr"/>
+      <c r="AS32" s="3" t="inlineStr"/>
+      <c r="AT32" s="3" t="inlineStr"/>
+      <c r="AU32" s="3" t="inlineStr"/>
+      <c r="AV32" s="3" t="inlineStr"/>
+      <c r="AW32" s="3" t="inlineStr"/>
+      <c r="AX32" s="3" t="inlineStr"/>
+      <c r="AY32" s="3" t="inlineStr"/>
+      <c r="AZ32" s="3" t="inlineStr"/>
+      <c r="BA32" s="3" t="inlineStr"/>
+      <c r="BB32" s="3" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="BC32" s="4" t="inlineStr">
+      <c r="BC32" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD32" s="4" t="inlineStr"/>
-      <c r="BE32" s="4" t="inlineStr">
+      <c r="BD32" s="3" t="inlineStr"/>
+      <c r="BE32" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF32" s="4" t="inlineStr"/>
-      <c r="BG32" s="4" t="inlineStr">
+      <c r="BF32" s="3" t="inlineStr"/>
+      <c r="BG32" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH32" s="4" t="inlineStr"/>
+      <c r="BH32" s="3" t="inlineStr"/>
+      <c r="BI32" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ32" s="3" t="inlineStr"/>
+      <c r="BK32" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Amazon $2.5 billion settlement expanded | How much you can get if you're eligible under revised order</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>0.097</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQNzdabGZicFI5bVRmUlp4dThNblI0bkJTNXR4WDJJVUN2cndvNHdLUDdnMlNGMEdTZmpsdGg5eWdkTkNFeHhpTmFvSE5mRlpyalN2ZkZKcG44N0s4T1h3T3VrRXB0R3FuZTNQVnVsVUtROXdIbkxWMzByN3lBM0tibXFOOHc1cGFEU0E?oc=5</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>KCRA</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr"/>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>14886156062848289edaa8ffe9e4a95e</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>90fdf92ba70ad5b40c336f9c</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>a15ea53dd887ca27b411aa11</t>
+        </is>
+      </c>
+      <c r="AE33" s="3" t="inlineStr"/>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr"/>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr"/>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr"/>
+      <c r="AM33" s="3" t="inlineStr"/>
+      <c r="AN33" s="3" t="inlineStr"/>
+      <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t>0.097</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr"/>
-      <c r="Q33" s="4" t="inlineStr"/>
-      <c r="R33" s="4" t="inlineStr"/>
-      <c r="S33" s="4" t="inlineStr"/>
-      <c r="T33" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U33" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQNzdabGZicFI5bVRmUlp4dThNblI0bkJTNXR4WDJJVUN2cndvNHdLUDdnMlNGMEdTZmpsdGg5eWdkTkNFeHhpTmFvSE5mRlpyalN2ZkZKcG44N0s4T1h3T3VrRXB0R3FuZTNQVnVsVUtROXdIbkxWMzByN3lBM0tibXFOOHc1cGFEU0E?oc=5</t>
-        </is>
-      </c>
-      <c r="V33" s="4" t="inlineStr">
-        <is>
-          <t>KCRA</t>
-        </is>
-      </c>
-      <c r="W33" s="4" t="inlineStr"/>
-      <c r="X33" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y33" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z33" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA33" s="4" t="inlineStr"/>
-      <c r="AB33" s="4" t="inlineStr"/>
-      <c r="AC33" s="4" t="inlineStr">
-        <is>
-          <t>90fdf92ba70ad5b40c336f9c</t>
-        </is>
-      </c>
-      <c r="AD33" s="4" t="inlineStr">
-        <is>
-          <t>a15ea53dd887ca27b411aa11</t>
-        </is>
-      </c>
-      <c r="AE33" s="4" t="inlineStr"/>
-      <c r="AF33" s="4" t="inlineStr"/>
-      <c r="AG33" s="4" t="inlineStr"/>
-      <c r="AH33" s="4" t="inlineStr"/>
-      <c r="AI33" s="4" t="inlineStr"/>
-      <c r="AJ33" s="4" t="inlineStr"/>
-      <c r="AK33" s="4" t="inlineStr"/>
-      <c r="AL33" s="4" t="inlineStr"/>
-      <c r="AM33" s="4" t="inlineStr"/>
-      <c r="AN33" s="4" t="inlineStr"/>
-      <c r="AO33" s="4" t="inlineStr"/>
-      <c r="AP33" s="4" t="inlineStr"/>
-      <c r="AQ33" s="4" t="inlineStr"/>
-      <c r="AR33" s="4" t="inlineStr"/>
-      <c r="AS33" s="4" t="inlineStr"/>
-      <c r="AT33" s="4" t="inlineStr"/>
-      <c r="AU33" s="4" t="inlineStr"/>
-      <c r="AV33" s="4" t="inlineStr"/>
-      <c r="AW33" s="4" t="inlineStr"/>
-      <c r="AX33" s="4" t="inlineStr"/>
-      <c r="AY33" s="4" t="inlineStr"/>
-      <c r="AZ33" s="4" t="inlineStr"/>
-      <c r="BA33" s="4" t="inlineStr"/>
-      <c r="BB33" s="4" t="inlineStr">
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr"/>
+      <c r="AS33" s="3" t="inlineStr"/>
+      <c r="AT33" s="3" t="inlineStr"/>
+      <c r="AU33" s="3" t="inlineStr"/>
+      <c r="AV33" s="3" t="inlineStr"/>
+      <c r="AW33" s="3" t="inlineStr"/>
+      <c r="AX33" s="3" t="inlineStr"/>
+      <c r="AY33" s="3" t="inlineStr"/>
+      <c r="AZ33" s="3" t="inlineStr"/>
+      <c r="BA33" s="3" t="inlineStr"/>
+      <c r="BB33" s="3" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="BC33" s="4" t="inlineStr">
+      <c r="BC33" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD33" s="4" t="inlineStr"/>
-      <c r="BE33" s="4" t="inlineStr">
+      <c r="BD33" s="3" t="inlineStr"/>
+      <c r="BE33" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF33" s="4" t="inlineStr"/>
-      <c r="BG33" s="4" t="inlineStr">
+      <c r="BF33" s="3" t="inlineStr"/>
+      <c r="BG33" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH33" s="4" t="inlineStr"/>
+      <c r="BH33" s="3" t="inlineStr"/>
+      <c r="BI33" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ33" s="3" t="inlineStr"/>
+      <c r="BK33" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>ABT</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Abbott Laboratories</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>2026-09-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Abbott Laboratories Stock (ABT) Opinions on Infant Formula Settlement</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr"/>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>0.049</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr"/>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr"/>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUGRiVDJNakk0RTIwRGhwT0phXzFLNjR4UHdqRWtua0lnNThOVXNMOS0yTHhFdUMwUkFHVkhmTGFXWWROczByc2dOZGRkV3pnSVZUSEV0Vi1raTJuSk1leVMxd21vdUVmSlRxQlNmUkh0UEs0RnF4MEdoU21wM2xUUXEtYjlEWWZvYW05UWhRdVdzRTlQZ0tjbGY4ZmVNV0F5QXRERA?oc=5</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>Quiver Quantitative</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr"/>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr"/>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>d5f4e99c7e054d3897b45d4e70525dce</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>fc07250b13f063c8b7366f3f</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr">
+        <is>
+          <t>80e019e60d7c1ec75cf31e1b</t>
+        </is>
+      </c>
+      <c r="AE34" s="3" t="inlineStr"/>
+      <c r="AF34" s="3" t="inlineStr"/>
+      <c r="AG34" s="3" t="inlineStr"/>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr"/>
+      <c r="AM34" s="3" t="inlineStr"/>
+      <c r="AN34" s="3" t="inlineStr"/>
+      <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>0.049</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="inlineStr"/>
-      <c r="Q34" s="4" t="inlineStr"/>
-      <c r="R34" s="4" t="inlineStr"/>
-      <c r="S34" s="4" t="inlineStr"/>
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUGRiVDJNakk0RTIwRGhwT0phXzFLNjR4UHdqRWtua0lnNThOVXNMOS0yTHhFdUMwUkFHVkhmTGFXWWROczByc2dOZGRkV3pnSVZUSEV0Vi1raTJuSk1leVMxd21vdUVmSlRxQlNmUkh0UEs0RnF4MEdoU21wM2xUUXEtYjlEWWZvYW05UWhRdVdzRTlQZ0tjbGY4ZmVNV0F5QXRERA?oc=5</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="inlineStr">
-        <is>
-          <t>Quiver Quantitative</t>
-        </is>
-      </c>
-      <c r="W34" s="4" t="inlineStr"/>
-      <c r="X34" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y34" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z34" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA34" s="4" t="inlineStr"/>
-      <c r="AB34" s="4" t="inlineStr"/>
-      <c r="AC34" s="4" t="inlineStr">
-        <is>
-          <t>fc07250b13f063c8b7366f3f</t>
-        </is>
-      </c>
-      <c r="AD34" s="4" t="inlineStr">
-        <is>
-          <t>80e019e60d7c1ec75cf31e1b</t>
-        </is>
-      </c>
-      <c r="AE34" s="4" t="inlineStr"/>
-      <c r="AF34" s="4" t="inlineStr"/>
-      <c r="AG34" s="4" t="inlineStr"/>
-      <c r="AH34" s="4" t="inlineStr"/>
-      <c r="AI34" s="4" t="inlineStr"/>
-      <c r="AJ34" s="4" t="inlineStr"/>
-      <c r="AK34" s="4" t="inlineStr"/>
-      <c r="AL34" s="4" t="inlineStr"/>
-      <c r="AM34" s="4" t="inlineStr"/>
-      <c r="AN34" s="4" t="inlineStr"/>
-      <c r="AO34" s="4" t="inlineStr"/>
-      <c r="AP34" s="4" t="inlineStr"/>
-      <c r="AQ34" s="4" t="inlineStr"/>
-      <c r="AR34" s="4" t="inlineStr"/>
-      <c r="AS34" s="4" t="inlineStr"/>
-      <c r="AT34" s="4" t="inlineStr"/>
-      <c r="AU34" s="4" t="inlineStr"/>
-      <c r="AV34" s="4" t="inlineStr"/>
-      <c r="AW34" s="4" t="inlineStr">
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr"/>
+      <c r="AS34" s="3" t="inlineStr"/>
+      <c r="AT34" s="3" t="inlineStr"/>
+      <c r="AU34" s="3" t="inlineStr"/>
+      <c r="AV34" s="3" t="inlineStr"/>
+      <c r="AW34" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX34" s="4" t="inlineStr"/>
-      <c r="AY34" s="4" t="inlineStr"/>
-      <c r="AZ34" s="4" t="inlineStr"/>
-      <c r="BA34" s="4" t="inlineStr"/>
-      <c r="BB34" s="4" t="inlineStr">
+      <c r="AX34" s="3" t="inlineStr"/>
+      <c r="AY34" s="3" t="inlineStr"/>
+      <c r="AZ34" s="3" t="inlineStr"/>
+      <c r="BA34" s="3" t="inlineStr"/>
+      <c r="BB34" s="3" t="inlineStr">
         <is>
           <t>ABT</t>
         </is>
       </c>
-      <c r="BC34" s="4" t="inlineStr">
+      <c r="BC34" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD34" s="4" t="inlineStr"/>
-      <c r="BE34" s="4" t="inlineStr">
+      <c r="BD34" s="3" t="inlineStr"/>
+      <c r="BE34" s="3" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
         </is>
       </c>
-      <c r="BF34" s="4" t="inlineStr">
+      <c r="BF34" s="3" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="BG34" s="4" t="inlineStr">
+      <c r="BG34" s="3" t="inlineStr">
         <is>
           <t>上市公司</t>
         </is>
       </c>
-      <c r="BH34" s="4" t="inlineStr"/>
+      <c r="BH34" s="3" t="inlineStr"/>
+      <c r="BI34" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ34" s="3" t="inlineStr"/>
+      <c r="BK34" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -6529,6 +7021,10 @@
         </is>
       </c>
       <c r="BH35" s="3" t="inlineStr"/>
+      <c r="BI35" s="3" t="inlineStr"/>
+      <c r="BJ35" s="3" t="inlineStr"/>
+      <c r="BK35" s="3" t="inlineStr"/>
+      <c r="BL35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -6691,6 +7187,10 @@
         </is>
       </c>
       <c r="BH36" s="3" t="inlineStr"/>
+      <c r="BI36" s="3" t="inlineStr"/>
+      <c r="BJ36" s="3" t="inlineStr"/>
+      <c r="BK36" s="3" t="inlineStr"/>
+      <c r="BL36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -6861,6 +7361,10 @@
         </is>
       </c>
       <c r="BH37" s="3" t="inlineStr"/>
+      <c r="BI37" s="3" t="inlineStr"/>
+      <c r="BJ37" s="3" t="inlineStr"/>
+      <c r="BK37" s="3" t="inlineStr"/>
+      <c r="BL37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -7031,6 +7535,10 @@
         </is>
       </c>
       <c r="BH38" s="3" t="inlineStr"/>
+      <c r="BI38" s="3" t="inlineStr"/>
+      <c r="BJ38" s="3" t="inlineStr"/>
+      <c r="BK38" s="3" t="inlineStr"/>
+      <c r="BL38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -7193,6 +7701,10 @@
         </is>
       </c>
       <c r="BH39" s="3" t="inlineStr"/>
+      <c r="BI39" s="3" t="inlineStr"/>
+      <c r="BJ39" s="3" t="inlineStr"/>
+      <c r="BK39" s="3" t="inlineStr"/>
+      <c r="BL39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -7363,6 +7875,10 @@
         </is>
       </c>
       <c r="BH40" s="3" t="inlineStr"/>
+      <c r="BI40" s="3" t="inlineStr"/>
+      <c r="BJ40" s="3" t="inlineStr"/>
+      <c r="BK40" s="3" t="inlineStr"/>
+      <c r="BL40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -7525,9 +8041,13 @@
         </is>
       </c>
       <c r="BH41" s="3" t="inlineStr"/>
+      <c r="BI41" s="3" t="inlineStr"/>
+      <c r="BJ41" s="3" t="inlineStr"/>
+      <c r="BK41" s="3" t="inlineStr"/>
+      <c r="BL41" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH41"/>
+  <autoFilter ref="A1:BL41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7538,7 +8058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BL11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7601,6 +8121,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7902,6 +8426,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -8074,6 +8618,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8244,168 +8792,176 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JBHT</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>J.B. Hunt</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-09-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Amazon Prime settlement expands: More consumers eligible for refunds up to $200</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>J.B. Hunt's Stock Plunges After Market Misprices Profit Warning</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>財測下修</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>0.899</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>'-0.959</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNRGM0WWxUbERMdnNUYVMzbDB0R1JsUHpGMk5Lc3V5UjBFTjRyVm1fajNReWNpcXNRc25xUVMwUzN3aXpYbmlWZmtMLWRtNlNMTE9ET1ZNRFhheTdMMXBfRk5ZTEF0OFplaGZOUk82XzNQY0Q1eVpIQl93UHhGbUVSMU1aMEM2Zkw4ajI5YWRVWmxsaFQtdm1SajhnNi1rWTZyNTFzRWN6aDNzaVUxQllLSTN5TUtYdFlfUUN4eDFrWFV6QW8?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>News4JAX</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>0fc24e64eb0939a1d337b0fe</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>edd52ac9baec10ec5afba764</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNNXBFUTBuVVZyTkt4VEs0VDg0aGJQNjdQb0NXQkFjZzVlRmprel9hcWt6R2tzTkwzUnRsbHF3MElXT1BJWnIyT2h1QVBNcF9fNjBfSFUzdjFJWlg2THNMNi0zbkhuNXNDUG9rZ1ZYX1JFMGExQWswUXY3YjdBZDRaQnlGZ1lZRUFsZ2tHLV82WGNkUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>EARNINGS_WARNING</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>profit warning</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>3623d5dfa89fc6681c3afc5a</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>f74ae452853c7fb50f57225e</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AK4" s="2" t="inlineStr"/>
+      <c r="AL4" s="2" t="inlineStr"/>
+      <c r="AM4" s="2" t="inlineStr"/>
+      <c r="AN4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AP4" s="2" t="inlineStr"/>
+      <c r="AQ4" s="2" t="inlineStr"/>
+      <c r="AR4" s="2" t="inlineStr"/>
+      <c r="AS4" s="2" t="inlineStr"/>
+      <c r="AT4" s="2" t="inlineStr"/>
+      <c r="AU4" s="2" t="inlineStr"/>
+      <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" s="2" t="inlineStr"/>
+      <c r="AX4" s="2" t="inlineStr"/>
+      <c r="AY4" s="2" t="inlineStr"/>
+      <c r="AZ4" s="2" t="inlineStr"/>
+      <c r="BA4" s="2" t="inlineStr"/>
+      <c r="BB4" s="2" t="inlineStr">
+        <is>
+          <t>JBHT</t>
+        </is>
+      </c>
+      <c r="BC4" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
+      <c r="BD4" s="2" t="inlineStr"/>
+      <c r="BE4" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF4" s="4" t="inlineStr"/>
-      <c r="BG4" s="4" t="inlineStr">
+      <c r="BF4" s="2" t="inlineStr"/>
+      <c r="BG4" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -8420,12 +8976,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt</t>
+          <t>PepsiCo, Inc.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -8435,7 +8991,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>J.B. Hunt's Stock Plunges After Market Misprices Profit Warning</t>
+          <t>Layoffs Affect All Employees At PepsiCo In Cheverly</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -8446,7 +9002,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>財測下修</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8472,7 +9028,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>'-0.959</t>
+          <t>'-0.956</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr"/>
@@ -8486,40 +9042,40 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNNXBFUTBuVVZyTkt4VEs0VDg0aGJQNjdQb0NXQkFjZzVlRmprel9hcWt6R2tzTkwzUnRsbHF3MElXT1BJWnIyT2h1QVBNcF9fNjBfSFUzdjFJWlg2THNMNi0zbkhuNXNDUG9rZ1ZYX1JFMGExQWswUXY3YjdBZDRaQnlGZ1lZRUFsZ2tHLV82WGNkUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPS2FmenJCZFJHc28wV3A2WFktMDl2bmR4UGpjSnRiQnNUMUktZWw2VDFGR1pVQXZWemhmYjlzU2htWWtmUUV1UDkwOUM0MTNUQ2FmUWMtTEZ2Z3VNUDU0QlhEajluYUwtdEVBZ203UGFTN3I0ZHFLUkh5UWhPcE1nb2RsMlRFd0tCSkhJOGZB?oc=5</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Patch</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>EARNINGS_WARNING</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>profit warning</t>
+          <t>layoff；layoffs</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3623d5dfa89fc6681c3afc5a</t>
+          <t>cb9313cd2fb740eacaaaebcb</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>f74ae452853c7fb50f57225e</t>
+          <t>597499bbf3820b4d41a8430a</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr"/>
@@ -8540,14 +9096,18 @@
       <c r="AT5" s="2" t="inlineStr"/>
       <c r="AU5" s="2" t="inlineStr"/>
       <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
       <c r="AX5" s="2" t="inlineStr"/>
       <c r="AY5" s="2" t="inlineStr"/>
       <c r="AZ5" s="2" t="inlineStr"/>
       <c r="BA5" s="2" t="inlineStr"/>
       <c r="BB5" s="2" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="BC5" s="2" t="inlineStr">
@@ -8558,186 +9118,222 @@
       <c r="BD5" s="2" t="inlineStr"/>
       <c r="BE5" s="2" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF5" s="2" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
       <c r="BG5" s="2" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>PepsiCo, Inc.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated Common Stock</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2026-09-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Layoffs Affect All Employees At PepsiCo In Cheverly</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Visa, Mastercard agree to $167.5M class action settlement: Are you eligible for a payout?</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>0.578</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPMUdfeHY3OUhzOTI0N2cwd1I5ck5tU21LYnBYTGFqVjZwQU81U2NoV2laY3MtenpHMlI2N1J1UWpNUUNTd25CSHA2U0ZTRjhSYkw2Qk5JSW50Z01HQ0pXbUtEckc3T3cyS3lueWVENU9FcDR5YXBfLTJ5ZzNZU0hZOENNSnpFaWZXdmlWaFQ2MGZPemx5T1dXWGxIM2pDTGNTOVpZLTZfMmh4NE0wdEZiUDRkb3BDVl9tNlljR2djVkdDMUVHLUhkWjMtZmdEOGtja3drbzVDOTJ2VUZvQkdOUDE4NA?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>KHOU</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>feb485e895ff479fa1c582b674c6692b</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>3510532871d2cfa2d2ebe2db</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>997d0b69c48f9ad583f30076</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>'-0.956</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPS2FmenJCZFJHc28wV3A2WFktMDl2bmR4UGpjSnRiQnNUMUktZWw2VDFGR1pVQXZWemhmYjlzU2htWWtmUUV1UDkwOUM0MTNUQ2FmUWMtTEZ2Z3VNUDU0QlhEajluYUwtdEVBZ203UGFTN3I0ZHFLUkh5UWhPcE1nb2RsMlRFd0tCSkhJOGZB?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Patch</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>cb9313cd2fb740eacaaaebcb</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>597499bbf3820b4d41a8430a</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="2" t="inlineStr">
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG6" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -8750,14 +9346,10 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -8767,7 +9359,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Amazon FTC settlement update: More Prime members qualify and payout increased to $200</t>
+          <t>Corpay to Pay $100 Million to Resolve FTC Allegations</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -8788,13 +9380,17 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -8804,7 +9400,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>0.933</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr"/>
@@ -8813,17 +9409,17 @@
       <c r="S7" s="4" t="inlineStr"/>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>主體證據不足</t>
         </is>
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPWm10V285QU4ydXZZTHhxcFg2bENfdTFIYzFrbjhRSWRpd0VVVnZHUERTTkNUb2lSQXJ1eDJzSi13RXNPeEg2MFZzR3Fwb3JZMC1zMWZoSkRXUkx2SXlyMDE1dHV3QmlVbmd5a1JiUy1VUldOZTlKRXg0akE1aDNRVUM0cG9HMEQ5Q3B0Umozc3M3NWVQdjYxRUNEdmxmbmI2WWI4d29TOHgzajRIbFllUE50RlNYVW84Ym51WmM4RmFPdGpHbGVXVFY0M29lbVF2Mm1mMGp1ONIB3wFBVV95cUxNY3M5Z01EbDR1UHdGWEpET3Q1eWgtZllNUkhQNXBUNkRkUFp6RlFkNWdmaXNsRGFNcHJNOHJuQ2ZzMzI5dXR5bTVncGhPd3BCX3ZkZ2EyRzNrTDJsTW9pRjFKWlNQQzNDLUNTaW94a2NGU0hZbHRTeVFjVlliOGt3dWRzN2VleEFhYnFSV2Z4azlOdEFGZWdWQTkzVUxPUmdYS1E1aFhTcXZkUXlOYWlsOHdkMHlwdUxnUWwyQlhVdW94TXRXTzJ3amwxZkY1ZGpCMkNDaDVFZ0VWcXd3WFVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxON2N5NGNVUEhwWWJ6NGZtWEtOOXJvNkZoQ3NjNVFCSHRkOVpfeGRKZFE0VlVrU0N5XzlyWDU3cnNDZ0xNYWktUDBmRzVjUGtiaV9Kc1lvQmsyX1c3VVo0S3hrNFZZQTl1SHdNMTdYOTZsN3BFOU5ONHBWa0xiVUwzdm5GZU5jenlFdnhsZnNIam85Yi1jdTdWUjQ5UQ?oc=5</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>NBC Connecticut</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="W7" s="4" t="inlineStr"/>
@@ -8839,19 +9435,23 @@
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>FTC</t>
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>f9c2c41e84d44272a0f0c95ac8d183a6</t>
+        </is>
+      </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>19458ffd5127974021f4396b</t>
+          <t>ae25e2a980721ffff21bb447</t>
         </is>
       </c>
       <c r="AD7" s="4" t="inlineStr">
         <is>
-          <t>e01a8a51d5d5baea7830f612</t>
+          <t>769df537c0dad0a13fcbec07</t>
         </is>
       </c>
       <c r="AE7" s="4" t="inlineStr"/>
@@ -8864,7 +9464,11 @@
       <c r="AL7" s="4" t="inlineStr"/>
       <c r="AM7" s="4" t="inlineStr"/>
       <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="4" t="inlineStr"/>
       <c r="AQ7" s="4" t="inlineStr"/>
       <c r="AR7" s="4" t="inlineStr"/>
@@ -8879,27 +9483,47 @@
       <c r="BA7" s="4" t="inlineStr"/>
       <c r="BB7" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="BC7" s="4" t="inlineStr">
         <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="4" t="inlineStr"/>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD7" s="4" t="inlineStr">
+        <is>
+          <t>CPAY</t>
+        </is>
+      </c>
       <c r="BE7" s="4" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr"/>
-      <c r="BG7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG7" s="4" t="inlineStr"/>
       <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -8914,12 +9538,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated Common Stock</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -8929,7 +9553,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Visa, Mastercard agree to $167.5M class action settlement: Are you eligible for a payout?</t>
+          <t>Paramount in talks to settle antitrust lawsuit blocking WBD deal</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -8940,7 +9564,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -8950,13 +9574,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -8966,7 +9594,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>'-0.683</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr"/>
@@ -8980,12 +9608,12 @@
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPMUdfeHY3OUhzOTI0N2cwd1I5ck5tU21LYnBYTGFqVjZwQU81U2NoV2laY3MtenpHMlI2N1J1UWpNUUNTd25CSHA2U0ZTRjhSYkw2Qk5JSW50Z01HQ0pXbUtEckc3T3cyS3lueWVENU9FcDR5YXBfLTJ5ZzNZU0hZOENNSnpFaWZXdmlWaFQ2MGZPemx5T1dXWGxIM2pDTGNTOVpZLTZfMmh4NE0wdEZiUDRkb3BDVl9tNlljR2djVkdDMUVHLUhkWjMtZmdEOGtja3drbzVDOTJ2VUZvQkdOUDE4NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPUzRma0VEM2VyTHpCQzg1Z1k1RmVsUXhES25JcVMydUFkS216MnVTcHhQX3lhaVd4bC1rZnVDOFZtOE9Rb3ZIT2J0ckRLX3ByU0doLVhxZ3NTTFBYVXpGem9sQUNTdkVNS1VPOU5zZHBOZ1h5cjI5VGlha3R0Q2xyVC1hN2E?oc=5</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>KHOU</t>
+          <t>Financial Times</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr"/>
@@ -8996,24 +9624,28 @@
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z8" s="4" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>antitrust</t>
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>080368e1826548a185195ca8fefea84a</t>
+        </is>
+      </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
-          <t>3510532871d2cfa2d2ebe2db</t>
+          <t>bc328f72682b113464f72997</t>
         </is>
       </c>
       <c r="AD8" s="4" t="inlineStr">
         <is>
-          <t>997d0b69c48f9ad583f30076</t>
+          <t>810c4e106a4cdc3184eae971</t>
         </is>
       </c>
       <c r="AE8" s="4" t="inlineStr"/>
@@ -9026,7 +9658,11 @@
       <c r="AL8" s="4" t="inlineStr"/>
       <c r="AM8" s="4" t="inlineStr"/>
       <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="4" t="inlineStr"/>
       <c r="AQ8" s="4" t="inlineStr"/>
       <c r="AR8" s="4" t="inlineStr"/>
@@ -9034,18 +9670,14 @@
       <c r="AT8" s="4" t="inlineStr"/>
       <c r="AU8" s="4" t="inlineStr"/>
       <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW8" s="4" t="inlineStr"/>
       <c r="AX8" s="4" t="inlineStr"/>
       <c r="AY8" s="4" t="inlineStr"/>
       <c r="AZ8" s="4" t="inlineStr"/>
       <c r="BA8" s="4" t="inlineStr"/>
       <c r="BB8" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="BC8" s="4" t="inlineStr">
@@ -9056,20 +9688,28 @@
       <c r="BD8" s="4" t="inlineStr"/>
       <c r="BE8" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF8" s="4" t="inlineStr"/>
       <c r="BG8" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -9082,10 +9722,14 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>BlackRock, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -9095,7 +9739,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Corpay to Pay $100 Million to Resolve FTC Allegations</t>
+          <t>DOJ weighs joining state antitrust suit against BlackRock and State Street -report</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -9106,7 +9750,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -9116,17 +9760,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -9136,7 +9780,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>'-0.489</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr"/>
@@ -9145,12 +9789,12 @@
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="4" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U9" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxON2N5NGNVUEhwWWJ6NGZtWEtOOXJvNkZoQ3NjNVFCSHRkOVpfeGRKZFE0VlVrU0N5XzlyWDU3cnNDZ0xNYWktUDBmRzVjUGtiaV9Kc1lvQmsyX1c3VVo0S3hrNFZZQTl1SHdNMTdYOTZsN3BFOU5ONHBWa0xiVUwzdm5GZU5jenlFdnhsZnNIam85Yi1jdTdWUjQ5UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNQVJHaTVDdXZFdFoxOTF2UnBSN2t1bzdhVTNkMzB5SVFWZThnbXdiR084bG80LTQ5UzNJLWU3cmFoc2RfR0htTnh4TDRESHdjZWdEVGZzMjd1VXh6ZGtWU1NWY1VyNGZYaEVwdU5yLUx6aGtIbU5fU3Y2MmZMdGFKWXQ0alo2MklGNVF1UnlBUWxDem9TeUYwMHRIUExySlAx?oc=5</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
@@ -9166,24 +9810,28 @@
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z9" s="4" t="inlineStr">
         <is>
-          <t>FTC</t>
+          <t>antitrust</t>
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>adce91ba1d434f38a5baaf8245f1c011</t>
+        </is>
+      </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
-          <t>ae25e2a980721ffff21bb447</t>
+          <t>083b3b5318369b358a750650</t>
         </is>
       </c>
       <c r="AD9" s="4" t="inlineStr">
         <is>
-          <t>769df537c0dad0a13fcbec07</t>
+          <t>e49d044dd63409204885d9eb</t>
         </is>
       </c>
       <c r="AE9" s="4" t="inlineStr"/>
@@ -9198,7 +9846,7 @@
       <c r="AN9" s="4" t="inlineStr"/>
       <c r="AO9" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP9" s="4" t="inlineStr"/>
@@ -9208,26 +9856,26 @@
       <c r="AT9" s="4" t="inlineStr"/>
       <c r="AU9" s="4" t="inlineStr"/>
       <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX9" s="4" t="inlineStr"/>
       <c r="AY9" s="4" t="inlineStr"/>
       <c r="AZ9" s="4" t="inlineStr"/>
       <c r="BA9" s="4" t="inlineStr"/>
       <c r="BB9" s="4" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="BC9" s="4" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD9" s="4" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD9" s="4" t="inlineStr"/>
       <c r="BE9" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
@@ -9238,8 +9886,24 @@
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="4" t="inlineStr"/>
+      <c r="BG9" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
       <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -9254,12 +9918,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Elevance Health, Inc. Common Stock</t>
+          <t>BlackRock, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -9269,7 +9933,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Elevance Health sued again over out-of-network penalty</t>
+          <t>DOJ Weighs Joining Texas BlackRock, State Street Antitrust Case</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -9280,7 +9944,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -9290,13 +9954,17 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -9306,7 +9974,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>'-0.921</t>
+          <t>'-0.297</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr"/>
@@ -9320,12 +9988,12 @@
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQS1pxV1FvM3FTdlRxVnhJSmVjZlY0RXFMQ2FqV21sczQ3TDJjZ1FqYU9kdGJLMHgxVTVhd0dYZEdfbkNYNldGZ2t1N0UtUTB2QjhlUXk5S1V1cWFSM1BneHRNN3lBQ2NLOGUwcVZIVjVxd2RSaTlsbGoyM0ptWUNXT0hJZGlKdEVNRU0xUUlnUHQ3LTBfbG9NWkhpcUxLbWpCOEVz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQMFROcDBnSlBjN2QyaGFSUnhVWkN1UmxMTWJFRE5VZkswdHBfN1NNMTlzSjNtXzJuWURwV1dycXdNUHdNMlhhUjVxM0JoV2VxNjlOcmNLU3A3Y01FdWlBZF85ZjZwZlNlOFVHNDdtcU42aERURlhvUFd4Q2dfNDJNVm8wS2dSX0g0c0Y1b2ZhSVNZSVFmN0tsZXczRmFMVy1ZU0syQQ?oc=5</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>Modern Healthcare</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr"/>
@@ -9336,24 +10004,28 @@
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z10" s="4" t="inlineStr">
         <is>
-          <t>penalty</t>
+          <t>antitrust</t>
         </is>
       </c>
       <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AB10" s="4" t="inlineStr">
+        <is>
+          <t>32fad879074b4e279a17274ae73b62c8</t>
+        </is>
+      </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
-          <t>5ef77219c82af0a31b781c5e</t>
+          <t>d72536a7bbcfac4b030ef4df</t>
         </is>
       </c>
       <c r="AD10" s="4" t="inlineStr">
         <is>
-          <t>6685c6a98dabcf0e53e4ec02</t>
+          <t>ecc65a4fad49a3e825adac1f</t>
         </is>
       </c>
       <c r="AE10" s="4" t="inlineStr"/>
@@ -9366,7 +10038,11 @@
       <c r="AL10" s="4" t="inlineStr"/>
       <c r="AM10" s="4" t="inlineStr"/>
       <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
+      <c r="AO10" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="4" t="inlineStr"/>
       <c r="AQ10" s="4" t="inlineStr"/>
       <c r="AR10" s="4" t="inlineStr"/>
@@ -9385,7 +10061,7 @@
       <c r="BA10" s="4" t="inlineStr"/>
       <c r="BB10" s="4" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="BC10" s="4" t="inlineStr">
@@ -9410,6 +10086,18 @@
         </is>
       </c>
       <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BI10" s="4" t="inlineStr"/>
+      <c r="BJ10" s="4" t="inlineStr"/>
+      <c r="BK10" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -9424,12 +10112,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -9439,7 +10127,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Paramount in talks to settle antitrust lawsuit blocking WBD deal</t>
+          <t>Corpay Agrees to Settle FTC Matter</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -9450,7 +10138,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>反壟斷調查</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -9460,13 +10148,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -9476,7 +10168,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>'-0.683</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr"/>
@@ -9485,17 +10177,17 @@
       <c r="S11" s="4" t="inlineStr"/>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>主體證據不足</t>
         </is>
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPUzRma0VEM2VyTHpCQzg1Z1k1RmVsUXhES25JcVMydUFkS216MnVTcHhQX3lhaVd4bC1rZnVDOFZtOE9Rb3ZIT2J0ckRLX3ByU0doLVhxZ3NTTFBYVXpGem9sQUNTdkVNS1VPOU5zZHBOZ1h5cjI5VGlha3R0Q2xyVC1hN2E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOcVlBMUdJMHNyVGhEVk93ckFOdWZyNTZpZTFselF3dnJXMnlpeFFJMjNKNUtmcWpKR2JNeGFKLW9RWTd6c05uYjA3bUNQUTc1b2pMYVcweTV2MFRyTTNvS1NVZHNxNHB1WV91OUp3NXMxSFgwbUZPNXNOZk5HU1M4R0g1WGZRMnNIM1dGWVJWX2syM2F6d1k0bGQ2NlE?oc=5</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>Financial Times</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr"/>
@@ -9506,24 +10198,28 @@
       </c>
       <c r="Y11" s="4" t="inlineStr">
         <is>
-          <t>ANTITRUST_INVESTIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z11" s="4" t="inlineStr">
         <is>
-          <t>antitrust</t>
+          <t>FTC</t>
         </is>
       </c>
       <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>a567ea6c2e324a5a93f8179b2d7f5220</t>
+        </is>
+      </c>
       <c r="AC11" s="4" t="inlineStr">
         <is>
-          <t>bc328f72682b113464f72997</t>
+          <t>c35e8f22bda649ec16865913</t>
         </is>
       </c>
       <c r="AD11" s="4" t="inlineStr">
         <is>
-          <t>810c4e106a4cdc3184eae971</t>
+          <t>7264deeee7c659f317b1d52b</t>
         </is>
       </c>
       <c r="AE11" s="4" t="inlineStr"/>
@@ -9536,7 +10232,11 @@
       <c r="AL11" s="4" t="inlineStr"/>
       <c r="AM11" s="4" t="inlineStr"/>
       <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="4" t="inlineStr"/>
       <c r="AQ11" s="4" t="inlineStr"/>
       <c r="AR11" s="4" t="inlineStr"/>
@@ -9551,1536 +10251,50 @@
       <c r="BA11" s="4" t="inlineStr"/>
       <c r="BB11" s="4" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="BC11" s="4" t="inlineStr">
         <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="4" t="inlineStr"/>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD11" s="4" t="inlineStr">
+        <is>
+          <t>CPAY</t>
+        </is>
+      </c>
       <c r="BE11" s="4" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF11" s="4" t="inlineStr"/>
-      <c r="BG11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG11" s="4" t="inlineStr"/>
       <c r="BH11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>BLK</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>BlackRock, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>DOJ weighs joining state antitrust suit against BlackRock and State Street -report</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>'-0.489</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNQVJHaTVDdXZFdFoxOTF2UnBSN2t1bzdhVTNkMzB5SVFWZThnbXdiR084bG80LTQ5UzNJLWU3cmFoc2RfR0htTnh4TDRESHdjZWdEVGZzMjd1VXh6ZGtWU1NWY1VyNGZYaEVwdU5yLUx6aGtIbU5fU3Y2MmZMdGFKWXQ0alo2MklGNVF1UnlBUWxDem9TeUYwMHRIUExySlAx?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>083b3b5318369b358a750650</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>e49d044dd63409204885d9eb</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>BLK</t>
-        </is>
-      </c>
-      <c r="BC12" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Mastercard Incorporated Common Stock</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Visa, Mastercard $167.5 million settlement could mean money for ATM users. Who qualifies.</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>'-0.486</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNVWtmbzlqT1pvM0k5bXJyMmJzSzZKNXU5bmNsSUoxNlZBSW9SOTlDTHdmUWZoMGo0ZEJleTEzTlgxWDg2VlBrMmJZTDJsQUktcVBEelRBTWs0cnNJeFJMWXlldWdJV3F5N0tUVzREY2hCRnd3OHJLZzJfS01CNEVlbkhBMC05R3RPdThqOWxoRXVJanBHWllvOUdvX041azJ0TzJIUjRnNXZkSUh2ZXpnM1pLSmtMTkRlSFJyMDZtaVFMUnp4dUUxVEpCN2RsU0ZDaHpnVVlvUEZEUDBFNkRXRXczM3lqMmFneUJadDRhbw?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>43b436b1305690f1d50e59b0</t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t>0bda3f4d7ae943fc690ebc6a</t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="4" t="inlineStr"/>
-      <c r="AS13" s="4" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="4" t="inlineStr"/>
-      <c r="AZ13" s="4" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="BC13" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="4" t="inlineStr"/>
-      <c r="BE13" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG13" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Walmart Inc.</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>The Morning Risk Report: Senators Ask FTC to Probe Walmart and Amazon Over Bots’ ‘Made in America’ Data</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>'-0.477</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPMGVVNVRSaldHUXlHOFNEZ0c4d0RFYnZnaGd2Y21id05GMk9Wb0E1OHJZTW42UHRITU9PR05yOHFuMG9fVl85UThtSkRwTFFWNjhBc0VVSnpzTG9VMnR2b2dvWlhTc1FjbnkzRFQ5aGRfQl95a0pOOTZ5dXBxWE9TNjF4TzZHbU4tVUN1QTVzRWZUM1BIQ0lsZXR4Wkd4WEhGMGdnNDlOUWtmNG41bXh6X1RlMmhHaHRxdXR4b195U2p0QlZESnBPMTFXS2JXMWQtRXp3ampVZEZ3WmF2MVpndDBIZ1ZGcGs?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>WSJ</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>8c4eb03572356403ee2a4859</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>4d32c640b9c8873434fc9a9d</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr"/>
-      <c r="AP14" s="4" t="inlineStr"/>
-      <c r="AQ14" s="4" t="inlineStr"/>
-      <c r="AR14" s="4" t="inlineStr"/>
-      <c r="AS14" s="4" t="inlineStr"/>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX14" s="4" t="inlineStr"/>
-      <c r="AY14" s="4" t="inlineStr"/>
-      <c r="AZ14" s="4" t="inlineStr"/>
-      <c r="BA14" s="4" t="inlineStr"/>
-      <c r="BB14" s="4" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="BC14" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD14" s="4" t="inlineStr"/>
-      <c r="BE14" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG14" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>BLK</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>BlackRock, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>DOJ Weighs Joining Texas BlackRock, State Street Antitrust Case</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>'-0.297</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQMFROcDBnSlBjN2QyaGFSUnhVWkN1UmxMTWJFRE5VZkswdHBfN1NNMTlzSjNtXzJuWURwV1dycXdNUHdNMlhhUjVxM0JoV2VxNjlOcmNLU3A3Y01FdWlBZF85ZjZwZlNlOFVHNDdtcU42aERURlhvUFd4Q2dfNDJNVm8wS2dSX0g0c0Y1b2ZhSVNZSVFmN0tsZXczRmFMVy1ZU0syQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>Bloomberg Law News</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>d72536a7bbcfac4b030ef4df</t>
-        </is>
-      </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>ecc65a4fad49a3e825adac1f</t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr"/>
-      <c r="AF15" s="4" t="inlineStr"/>
-      <c r="AG15" s="4" t="inlineStr"/>
-      <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="inlineStr"/>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr"/>
-      <c r="AL15" s="4" t="inlineStr"/>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr"/>
-      <c r="AP15" s="4" t="inlineStr"/>
-      <c r="AQ15" s="4" t="inlineStr"/>
-      <c r="AR15" s="4" t="inlineStr"/>
-      <c r="AS15" s="4" t="inlineStr"/>
-      <c r="AT15" s="4" t="inlineStr"/>
-      <c r="AU15" s="4" t="inlineStr"/>
-      <c r="AV15" s="4" t="inlineStr"/>
-      <c r="AW15" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX15" s="4" t="inlineStr"/>
-      <c r="AY15" s="4" t="inlineStr"/>
-      <c r="AZ15" s="4" t="inlineStr"/>
-      <c r="BA15" s="4" t="inlineStr"/>
-      <c r="BB15" s="4" t="inlineStr">
-        <is>
-          <t>BLK</t>
-        </is>
-      </c>
-      <c r="BC15" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD15" s="4" t="inlineStr"/>
-      <c r="BE15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG15" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Corpay</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Corpay Agrees to Settle FTC Matter</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>0.015</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOcVlBMUdJMHNyVGhEVk93ckFOdWZyNTZpZTFselF3dnJXMnlpeFFJMjNKNUtmcWpKR2JNeGFKLW9RWTd6c05uYjA3bUNQUTc1b2pMYVcweTV2MFRyTTNvS1NVZHNxNHB1WV91OUp3NXMxSFgwbUZPNXNOZk5HU1M4R0g1WGZRMnNIM1dGWVJWX2syM2F6d1k0bGQ2NlE?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>c35e8f22bda649ec16865913</t>
-        </is>
-      </c>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>7264deeee7c659f317b1d52b</t>
-        </is>
-      </c>
-      <c r="AE16" s="4" t="inlineStr"/>
-      <c r="AF16" s="4" t="inlineStr"/>
-      <c r="AG16" s="4" t="inlineStr"/>
-      <c r="AH16" s="4" t="inlineStr"/>
-      <c r="AI16" s="4" t="inlineStr"/>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="4" t="inlineStr"/>
-      <c r="AL16" s="4" t="inlineStr"/>
-      <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP16" s="4" t="inlineStr"/>
-      <c r="AQ16" s="4" t="inlineStr"/>
-      <c r="AR16" s="4" t="inlineStr"/>
-      <c r="AS16" s="4" t="inlineStr"/>
-      <c r="AT16" s="4" t="inlineStr"/>
-      <c r="AU16" s="4" t="inlineStr"/>
-      <c r="AV16" s="4" t="inlineStr"/>
-      <c r="AW16" s="4" t="inlineStr"/>
-      <c r="AX16" s="4" t="inlineStr"/>
-      <c r="AY16" s="4" t="inlineStr"/>
-      <c r="AZ16" s="4" t="inlineStr"/>
-      <c r="BA16" s="4" t="inlineStr"/>
-      <c r="BB16" s="4" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
-      <c r="BC16" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD16" s="4" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
-      <c r="BE16" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG16" s="4" t="inlineStr"/>
-      <c r="BH16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Amazon Prime customers could receive up to $200 in refunds under expanded FTC settlement</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>0.057</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE4wblJEQzB3cXV4NmZuc0w4bmstRzFJcXYtSmNJVGVYRXptUklRUWExeDB3UUpGTDZPMWV2THZtTVdIWDhBZUxYalVLOGlUM3dKeXBpbzVMVWNCWkhRN1ZGNHV5SGl4alBUTnVpNEthTGVLZm9kb1Y4?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t>MyNorthwest.com</t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z17" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr"/>
-      <c r="AC17" s="4" t="inlineStr">
-        <is>
-          <t>d399e06478c17d4b082ba900</t>
-        </is>
-      </c>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t>95ebe81054411e953092304e</t>
-        </is>
-      </c>
-      <c r="AE17" s="4" t="inlineStr"/>
-      <c r="AF17" s="4" t="inlineStr"/>
-      <c r="AG17" s="4" t="inlineStr"/>
-      <c r="AH17" s="4" t="inlineStr"/>
-      <c r="AI17" s="4" t="inlineStr"/>
-      <c r="AJ17" s="4" t="inlineStr"/>
-      <c r="AK17" s="4" t="inlineStr"/>
-      <c r="AL17" s="4" t="inlineStr"/>
-      <c r="AM17" s="4" t="inlineStr"/>
-      <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
-      <c r="AP17" s="4" t="inlineStr"/>
-      <c r="AQ17" s="4" t="inlineStr"/>
-      <c r="AR17" s="4" t="inlineStr"/>
-      <c r="AS17" s="4" t="inlineStr"/>
-      <c r="AT17" s="4" t="inlineStr"/>
-      <c r="AU17" s="4" t="inlineStr"/>
-      <c r="AV17" s="4" t="inlineStr"/>
-      <c r="AW17" s="4" t="inlineStr"/>
-      <c r="AX17" s="4" t="inlineStr"/>
-      <c r="AY17" s="4" t="inlineStr"/>
-      <c r="AZ17" s="4" t="inlineStr"/>
-      <c r="BA17" s="4" t="inlineStr"/>
-      <c r="BB17" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC17" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD17" s="4" t="inlineStr"/>
-      <c r="BE17" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF17" s="4" t="inlineStr"/>
-      <c r="BG17" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Amazon Prime customers may be eligible to receive $200 as settlement grows</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPTF9jaHpTRUh6QjlHbm5aMVJfa2pCQVdYTlFINmd1U0pQVzlRSnBNNmdEYmFBMjBQVHFwZ0hhSGxXalNhTHFaU29WTGJjYnJSYVU0dGl3ZnVVSmQ0YkZMN05UY3A2VDZHbkxPc2lKX29aYThKeTJWYWFGX3hZRnYwa0tHMFoycHRRbEt4XzJSdWJObGo1d1ZyaW83RFk?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>Dallas News</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z18" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="inlineStr">
-        <is>
-          <t>cf3548bf28669271ba85d455</t>
-        </is>
-      </c>
-      <c r="AD18" s="4" t="inlineStr">
-        <is>
-          <t>610a60c13836ba4e753cc26d</t>
-        </is>
-      </c>
-      <c r="AE18" s="4" t="inlineStr"/>
-      <c r="AF18" s="4" t="inlineStr"/>
-      <c r="AG18" s="4" t="inlineStr"/>
-      <c r="AH18" s="4" t="inlineStr"/>
-      <c r="AI18" s="4" t="inlineStr"/>
-      <c r="AJ18" s="4" t="inlineStr"/>
-      <c r="AK18" s="4" t="inlineStr"/>
-      <c r="AL18" s="4" t="inlineStr"/>
-      <c r="AM18" s="4" t="inlineStr"/>
-      <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
-      <c r="AP18" s="4" t="inlineStr"/>
-      <c r="AQ18" s="4" t="inlineStr"/>
-      <c r="AR18" s="4" t="inlineStr"/>
-      <c r="AS18" s="4" t="inlineStr"/>
-      <c r="AT18" s="4" t="inlineStr"/>
-      <c r="AU18" s="4" t="inlineStr"/>
-      <c r="AV18" s="4" t="inlineStr"/>
-      <c r="AW18" s="4" t="inlineStr"/>
-      <c r="AX18" s="4" t="inlineStr"/>
-      <c r="AY18" s="4" t="inlineStr"/>
-      <c r="AZ18" s="4" t="inlineStr"/>
-      <c r="BA18" s="4" t="inlineStr"/>
-      <c r="BB18" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC18" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD18" s="4" t="inlineStr"/>
-      <c r="BE18" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF18" s="4" t="inlineStr"/>
-      <c r="BG18" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Amazon $2.5 billion settlement expanded | How much you can get if you're eligible under revised order</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>0.097</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQNzdabGZicFI5bVRmUlp4dThNblI0bkJTNXR4WDJJVUN2cndvNHdLUDdnMlNGMEdTZmpsdGg5eWdkTkNFeHhpTmFvSE5mRlpyalN2ZkZKcG44N0s4T1h3T3VrRXB0R3FuZTNQVnVsVUtROXdIbkxWMzByN3lBM0tibXFOOHc1cGFEU0E?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>KCRA</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z19" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="inlineStr">
-        <is>
-          <t>90fdf92ba70ad5b40c336f9c</t>
-        </is>
-      </c>
-      <c r="AD19" s="4" t="inlineStr">
-        <is>
-          <t>a15ea53dd887ca27b411aa11</t>
-        </is>
-      </c>
-      <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="inlineStr"/>
-      <c r="AG19" s="4" t="inlineStr"/>
-      <c r="AH19" s="4" t="inlineStr"/>
-      <c r="AI19" s="4" t="inlineStr"/>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
-      <c r="AP19" s="4" t="inlineStr"/>
-      <c r="AQ19" s="4" t="inlineStr"/>
-      <c r="AR19" s="4" t="inlineStr"/>
-      <c r="AS19" s="4" t="inlineStr"/>
-      <c r="AT19" s="4" t="inlineStr"/>
-      <c r="AU19" s="4" t="inlineStr"/>
-      <c r="AV19" s="4" t="inlineStr"/>
-      <c r="AW19" s="4" t="inlineStr"/>
-      <c r="AX19" s="4" t="inlineStr"/>
-      <c r="AY19" s="4" t="inlineStr"/>
-      <c r="AZ19" s="4" t="inlineStr"/>
-      <c r="BA19" s="4" t="inlineStr"/>
-      <c r="BB19" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC19" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD19" s="4" t="inlineStr"/>
-      <c r="BE19" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF19" s="4" t="inlineStr"/>
-      <c r="BG19" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Abbott Laboratories</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Abbott Laboratories Stock (ABT) Opinions on Infant Formula Settlement</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>0.049</t>
-        </is>
-      </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUGRiVDJNakk0RTIwRGhwT0phXzFLNjR4UHdqRWtua0lnNThOVXNMOS0yTHhFdUMwUkFHVkhmTGFXWWROczByc2dOZGRkV3pnSVZUSEV0Vi1raTJuSk1leVMxd21vdUVmSlRxQlNmUkh0UEs0RnF4MEdoU21wM2xUUXEtYjlEWWZvYW05UWhRdVdzRTlQZ0tjbGY4ZmVNV0F5QXRERA?oc=5</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>Quiver Quantitative</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="inlineStr"/>
-      <c r="X20" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y20" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z20" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr"/>
-      <c r="AC20" s="4" t="inlineStr">
-        <is>
-          <t>fc07250b13f063c8b7366f3f</t>
-        </is>
-      </c>
-      <c r="AD20" s="4" t="inlineStr">
-        <is>
-          <t>80e019e60d7c1ec75cf31e1b</t>
-        </is>
-      </c>
-      <c r="AE20" s="4" t="inlineStr"/>
-      <c r="AF20" s="4" t="inlineStr"/>
-      <c r="AG20" s="4" t="inlineStr"/>
-      <c r="AH20" s="4" t="inlineStr"/>
-      <c r="AI20" s="4" t="inlineStr"/>
-      <c r="AJ20" s="4" t="inlineStr"/>
-      <c r="AK20" s="4" t="inlineStr"/>
-      <c r="AL20" s="4" t="inlineStr"/>
-      <c r="AM20" s="4" t="inlineStr"/>
-      <c r="AN20" s="4" t="inlineStr"/>
-      <c r="AO20" s="4" t="inlineStr"/>
-      <c r="AP20" s="4" t="inlineStr"/>
-      <c r="AQ20" s="4" t="inlineStr"/>
-      <c r="AR20" s="4" t="inlineStr"/>
-      <c r="AS20" s="4" t="inlineStr"/>
-      <c r="AT20" s="4" t="inlineStr"/>
-      <c r="AU20" s="4" t="inlineStr"/>
-      <c r="AV20" s="4" t="inlineStr"/>
-      <c r="AW20" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX20" s="4" t="inlineStr"/>
-      <c r="AY20" s="4" t="inlineStr"/>
-      <c r="AZ20" s="4" t="inlineStr"/>
-      <c r="BA20" s="4" t="inlineStr"/>
-      <c r="BB20" s="4" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="BC20" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD20" s="4" t="inlineStr"/>
-      <c r="BE20" s="4" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
-        </is>
-      </c>
-      <c r="BF20" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG20" s="4" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH20" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|Ticker|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH20"/>
+  <autoFilter ref="A1:BL11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11091,7 +10305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11154,6 +10368,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11457,349 +10675,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Corpay</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Corpay to Pay $100 Million to Resolve FTC Allegations</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>0.131</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxON2N5NGNVUEhwWWJ6NGZtWEtOOXJvNkZoQ3NjNVFCSHRkOVpfeGRKZFE0VlVrU0N5XzlyWDU3cnNDZ0xNYWktUDBmRzVjUGtiaV9Kc1lvQmsyX1c3VVo0S3hrNFZZQTl1SHdNMTdYOTZsN3BFOU5ONHBWa0xiVUwzdm5GZU5jenlFdnhsZnNIam85Yi1jdTdWUjQ5UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="inlineStr">
-        <is>
-          <t>ae25e2a980721ffff21bb447</t>
-        </is>
-      </c>
-      <c r="AD2" s="4" t="inlineStr">
-        <is>
-          <t>769df537c0dad0a13fcbec07</t>
-        </is>
-      </c>
-      <c r="AE2" s="4" t="inlineStr"/>
-      <c r="AF2" s="4" t="inlineStr"/>
-      <c r="AG2" s="4" t="inlineStr"/>
-      <c r="AH2" s="4" t="inlineStr"/>
-      <c r="AI2" s="4" t="inlineStr"/>
-      <c r="AJ2" s="4" t="inlineStr"/>
-      <c r="AK2" s="4" t="inlineStr"/>
-      <c r="AL2" s="4" t="inlineStr"/>
-      <c r="AM2" s="4" t="inlineStr"/>
-      <c r="AN2" s="4" t="inlineStr"/>
-      <c r="AO2" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="4" t="inlineStr"/>
-      <c r="AQ2" s="4" t="inlineStr"/>
-      <c r="AR2" s="4" t="inlineStr"/>
-      <c r="AS2" s="4" t="inlineStr"/>
-      <c r="AT2" s="4" t="inlineStr"/>
-      <c r="AU2" s="4" t="inlineStr"/>
-      <c r="AV2" s="4" t="inlineStr"/>
-      <c r="AW2" s="4" t="inlineStr"/>
-      <c r="AX2" s="4" t="inlineStr"/>
-      <c r="AY2" s="4" t="inlineStr"/>
-      <c r="AZ2" s="4" t="inlineStr"/>
-      <c r="BA2" s="4" t="inlineStr"/>
-      <c r="BB2" s="4" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
-      <c r="BC2" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="4" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
-      <c r="BE2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="4" t="inlineStr"/>
-      <c r="BH2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Corpay</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Corpay Agrees to Settle FTC Matter</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>0.015</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOcVlBMUdJMHNyVGhEVk93ckFOdWZyNTZpZTFselF3dnJXMnlpeFFJMjNKNUtmcWpKR2JNeGFKLW9RWTd6c05uYjA3bUNQUTc1b2pMYVcweTV2MFRyTTNvS1NVZHNxNHB1WV91OUp3NXMxSFgwbUZPNXNOZk5HU1M4R0g1WGZRMnNIM1dGWVJWX2syM2F6d1k0bGQ2NlE?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>c35e8f22bda649ec16865913</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>7264deeee7c659f317b1d52b</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr"/>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="4" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
-      <c r="BE3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="4" t="inlineStr"/>
-      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH3"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11810,7 +10708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11873,6 +10771,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12176,9 +11078,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12189,7 +11111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12239,134 +11161,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -12376,46 +11298,80 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="3" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="3" t="inlineStr"/>
       <c r="Y2" s="3" t="inlineStr"/>
       <c r="Z2" s="3" t="inlineStr"/>
@@ -12424,12 +11380,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -12439,90 +11395,94 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -12532,94 +11492,94 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="3" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -12627,89 +11587,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="3" t="n">
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-18.xlsx
+++ b/news_daily/2026-09-18.xlsx
@@ -1101,13 +1101,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1156,7 +1160,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>7ac39f37b52743219d29ab840dce50d7</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>7ea8b4fed14244a4ae2b7807</t>
@@ -1177,7 +1185,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1223,8 +1235,16 @@
       <c r="BH3" s="2" t="inlineStr"/>
       <c r="BI3" s="2" t="inlineStr"/>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1260,28 +1280,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1321,7 +1345,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1330,7 +1354,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>2d7c5f01ebb541f7bff60eee0527878b</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>c9aff6f6e957868e76f8229a</t>
@@ -1351,7 +1379,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1395,10 +1427,22 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1449,13 +1493,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1504,7 +1552,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>38f988e3a7b14b02baa705fd2f14d0d8</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>aab42ea99dddc08d848d2283</t>
@@ -1525,7 +1577,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1571,8 +1627,16 @@
       <c r="BH5" s="2" t="inlineStr"/>
       <c r="BI5" s="2" t="inlineStr"/>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1608,28 +1672,32 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1669,7 +1737,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1678,7 +1746,11 @@
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>5d0fe00dceaa4e0293568afd928ff367</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>aab42ea99dddc08d848d2283</t>
@@ -1699,7 +1771,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="2" t="inlineStr"/>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="inlineStr"/>
@@ -1735,10 +1811,22 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1774,28 +1862,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1835,7 +1927,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1844,7 +1936,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>2d162759fefc4d2883fe2dbf6116977f</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>36642bee109569dadfd42271</t>
@@ -1865,7 +1961,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1909,10 +2009,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1963,13 +2075,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2018,7 +2134,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>a7ed611f2da54372b596e70f12191604</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>9add8bc696c2c9ad88d5e973</t>
@@ -2039,7 +2159,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2085,8 +2209,16 @@
       <c r="BH8" s="2" t="inlineStr"/>
       <c r="BI8" s="2" t="inlineStr"/>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2137,13 +2269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2192,7 +2328,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>c2f6d77e7caf436888825218dc5bfa6c</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>0d44bf6a953c2e479a4e1418</t>
@@ -2213,7 +2353,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2259,8 +2403,16 @@
       <c r="BH9" s="2" t="inlineStr"/>
       <c r="BI9" s="2" t="inlineStr"/>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2311,13 +2463,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2366,7 +2522,11 @@
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>adb181f9b7a64728b4e0238fa2eaffd4</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>bbd1ff1df744eab57bc353e5</t>
@@ -2387,7 +2547,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2433,8 +2597,16 @@
       <c r="BH10" s="2" t="inlineStr"/>
       <c r="BI10" s="2" t="inlineStr"/>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2485,13 +2657,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2540,7 +2716,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>6165dcccda45490e9acf0897f57d94a6</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>7725cfecb3552a6035d777c4</t>
@@ -2561,7 +2741,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2607,8 +2791,16 @@
       <c r="BH11" s="2" t="inlineStr"/>
       <c r="BI11" s="2" t="inlineStr"/>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2857,13 +3049,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2912,7 +3108,11 @@
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>22ca617bb60a446aab60dbb0e4a72301</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>c5fbc186aa4eee4a8b1195f3</t>
@@ -2933,7 +3133,11 @@
       <c r="AL13" s="2" t="inlineStr"/>
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="2" t="inlineStr"/>
       <c r="AQ13" s="2" t="inlineStr"/>
       <c r="AR13" s="2" t="inlineStr"/>
@@ -2979,8 +3183,16 @@
       <c r="BH13" s="2" t="inlineStr"/>
       <c r="BI13" s="2" t="inlineStr"/>
       <c r="BJ13" s="2" t="inlineStr"/>
-      <c r="BK13" s="2" t="inlineStr"/>
-      <c r="BL13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3031,13 +3243,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3086,7 +3302,11 @@
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>78bd91e29c474a7c9d3d5746bfdebe91</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>d4d28a3ec1f8c6aae8f1dda7</t>
@@ -3107,7 +3327,11 @@
       <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="2" t="inlineStr"/>
       <c r="AQ14" s="2" t="inlineStr"/>
       <c r="AR14" s="2" t="inlineStr"/>
@@ -3153,8 +3377,16 @@
       <c r="BH14" s="2" t="inlineStr"/>
       <c r="BI14" s="2" t="inlineStr"/>
       <c r="BJ14" s="2" t="inlineStr"/>
-      <c r="BK14" s="2" t="inlineStr"/>
-      <c r="BL14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3395,13 +3627,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3450,7 +3686,11 @@
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>8206196d3f7546b6bebf69219598fa5f</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>0f212391989981cba0fec98b</t>
@@ -3471,7 +3711,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3517,8 +3761,16 @@
       <c r="BH16" s="2" t="inlineStr"/>
       <c r="BI16" s="2" t="inlineStr"/>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3569,13 +3821,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3624,7 +3880,11 @@
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>c2c654f339b648249e80d2e3b3f82b34</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>273f93439704908bfa18db2e</t>
@@ -3645,7 +3905,11 @@
       <c r="AL17" s="2" t="inlineStr"/>
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="2" t="inlineStr"/>
       <c r="AQ17" s="2" t="inlineStr"/>
       <c r="AR17" s="2" t="inlineStr"/>
@@ -3691,8 +3955,16 @@
       <c r="BH17" s="2" t="inlineStr"/>
       <c r="BI17" s="2" t="inlineStr"/>
       <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -4108,28 +4380,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4169,7 +4445,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4178,7 +4454,11 @@
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>6b2b08e1ca7b4e288243a8a398b72de1</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>0f212391989981cba0fec98b</t>
@@ -4199,7 +4479,11 @@
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="2" t="inlineStr"/>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
@@ -4235,10 +4519,22 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -6982,28 +7278,32 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -7043,7 +7343,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -7052,7 +7352,11 @@
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr"/>
-      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>064134df2bb54de88ff92c5826e3991d</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>8748878684dedcac11081242</t>
@@ -7073,7 +7377,11 @@
       <c r="AL35" s="2" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr"/>
       <c r="AN35" s="2" t="inlineStr"/>
-      <c r="AO35" s="2" t="inlineStr"/>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP35" s="2" t="inlineStr"/>
       <c r="AQ35" s="2" t="inlineStr"/>
       <c r="AR35" s="2" t="inlineStr"/>
@@ -7109,10 +7417,22 @@
         </is>
       </c>
       <c r="BH35" s="2" t="inlineStr"/>
-      <c r="BI35" s="2" t="inlineStr"/>
+      <c r="BI35" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ35" s="2" t="inlineStr"/>
-      <c r="BK35" s="2" t="inlineStr"/>
-      <c r="BL35" s="2" t="inlineStr"/>
+      <c r="BK35" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7163,13 +7483,17 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -7218,7 +7542,11 @@
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr"/>
-      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>f39073a834fc46cba0560c778bfe95c6</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>172cfdc935d9398fd4bfd9f1</t>
@@ -7239,7 +7567,11 @@
       <c r="AL36" s="2" t="inlineStr"/>
       <c r="AM36" s="2" t="inlineStr"/>
       <c r="AN36" s="2" t="inlineStr"/>
-      <c r="AO36" s="2" t="inlineStr"/>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP36" s="2" t="inlineStr"/>
       <c r="AQ36" s="2" t="inlineStr"/>
       <c r="AR36" s="2" t="inlineStr"/>
@@ -7277,8 +7609,16 @@
       <c r="BH36" s="2" t="inlineStr"/>
       <c r="BI36" s="2" t="inlineStr"/>
       <c r="BJ36" s="2" t="inlineStr"/>
-      <c r="BK36" s="2" t="inlineStr"/>
-      <c r="BL36" s="2" t="inlineStr"/>
+      <c r="BK36" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7314,28 +7654,32 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7375,7 +7719,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -7384,7 +7728,11 @@
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr"/>
-      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>94453f342f0046b3929673c12f081b27</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>5551cee09f0eff1fb326c1f3</t>
@@ -7405,7 +7753,11 @@
       <c r="AL37" s="2" t="inlineStr"/>
       <c r="AM37" s="2" t="inlineStr"/>
       <c r="AN37" s="2" t="inlineStr"/>
-      <c r="AO37" s="2" t="inlineStr"/>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP37" s="2" t="inlineStr"/>
       <c r="AQ37" s="2" t="inlineStr"/>
       <c r="AR37" s="2" t="inlineStr"/>
@@ -7449,10 +7801,22 @@
         </is>
       </c>
       <c r="BH37" s="2" t="inlineStr"/>
-      <c r="BI37" s="2" t="inlineStr"/>
+      <c r="BI37" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ37" s="2" t="inlineStr"/>
-      <c r="BK37" s="2" t="inlineStr"/>
-      <c r="BL37" s="2" t="inlineStr"/>
+      <c r="BK37" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7503,13 +7867,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -7558,7 +7926,11 @@
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr"/>
-      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>059493898ece444eaba5772540f72933</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>6a66977c09b12df34e056e70</t>
@@ -7579,7 +7951,11 @@
       <c r="AL38" s="2" t="inlineStr"/>
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr"/>
-      <c r="AO38" s="2" t="inlineStr"/>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP38" s="2" t="inlineStr"/>
       <c r="AQ38" s="2" t="inlineStr"/>
       <c r="AR38" s="2" t="inlineStr"/>
@@ -7625,8 +8001,16 @@
       <c r="BH38" s="2" t="inlineStr"/>
       <c r="BI38" s="2" t="inlineStr"/>
       <c r="BJ38" s="2" t="inlineStr"/>
-      <c r="BK38" s="2" t="inlineStr"/>
-      <c r="BL38" s="2" t="inlineStr"/>
+      <c r="BK38" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7662,28 +8046,32 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -7723,7 +8111,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -7732,7 +8120,11 @@
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr"/>
-      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>a5848203a5a9464daaa2d68758541360</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>6a66977c09b12df34e056e70</t>
@@ -7753,7 +8145,11 @@
       <c r="AL39" s="2" t="inlineStr"/>
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr"/>
-      <c r="AO39" s="2" t="inlineStr"/>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP39" s="2" t="inlineStr"/>
       <c r="AQ39" s="2" t="inlineStr"/>
       <c r="AR39" s="2" t="inlineStr"/>
@@ -7789,10 +8185,22 @@
         </is>
       </c>
       <c r="BH39" s="2" t="inlineStr"/>
-      <c r="BI39" s="2" t="inlineStr"/>
+      <c r="BI39" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ39" s="2" t="inlineStr"/>
-      <c r="BK39" s="2" t="inlineStr"/>
-      <c r="BL39" s="2" t="inlineStr"/>
+      <c r="BK39" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7828,28 +8236,32 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -7889,7 +8301,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -7898,7 +8310,11 @@
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr"/>
-      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>babadf6a7c0f4a6aa87be3ef44125cf3</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
           <t>cf1b5e95c0f326fb057501fc</t>
@@ -7919,7 +8335,11 @@
       <c r="AL40" s="2" t="inlineStr"/>
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr"/>
-      <c r="AO40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP40" s="2" t="inlineStr"/>
       <c r="AQ40" s="2" t="inlineStr"/>
       <c r="AR40" s="2" t="inlineStr"/>
@@ -7963,10 +8383,22 @@
         </is>
       </c>
       <c r="BH40" s="2" t="inlineStr"/>
-      <c r="BI40" s="2" t="inlineStr"/>
+      <c r="BI40" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ40" s="2" t="inlineStr"/>
-      <c r="BK40" s="2" t="inlineStr"/>
-      <c r="BL40" s="2" t="inlineStr"/>
+      <c r="BK40" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8002,28 +8434,32 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -8063,7 +8499,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -8072,7 +8508,11 @@
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr"/>
-      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>fab98dcf00674bdfa1018356d1f00198</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>34a82f3cfe2f76a446341500</t>
@@ -8093,7 +8533,11 @@
       <c r="AL41" s="2" t="inlineStr"/>
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr"/>
-      <c r="AO41" s="2" t="inlineStr"/>
+      <c r="AO41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP41" s="2" t="inlineStr"/>
       <c r="AQ41" s="2" t="inlineStr"/>
       <c r="AR41" s="2" t="inlineStr"/>
@@ -8129,10 +8573,22 @@
         </is>
       </c>
       <c r="BH41" s="2" t="inlineStr"/>
-      <c r="BI41" s="2" t="inlineStr"/>
+      <c r="BI41" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ41" s="2" t="inlineStr"/>
-      <c r="BK41" s="2" t="inlineStr"/>
-      <c r="BL41" s="2" t="inlineStr"/>
+      <c r="BK41" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL41"/>

--- a/news_daily/2026-09-18.xlsx
+++ b/news_daily/2026-09-18.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$41</definedName>
@@ -27,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -66,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -74,21 +71,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4935,7 +4924,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>CPAY</t>
+        </is>
+      </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Corpay</t>
@@ -5099,7 +5092,7 @@
       <c r="BH23" s="4" t="inlineStr"/>
       <c r="BI23" s="4" t="inlineStr">
         <is>
-          <t>Event_Code|事件中文</t>
+          <t>Event_Code|Ticker|事件中文</t>
         </is>
       </c>
       <c r="BJ23" s="4" t="inlineStr"/>
@@ -9582,7 +9575,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>CPAY</t>
+        </is>
+      </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Corpay</t>
@@ -9746,7 +9743,7 @@
       <c r="BH5" s="4" t="inlineStr"/>
       <c r="BI5" s="4" t="inlineStr">
         <is>
-          <t>Event_Code|事件中文</t>
+          <t>Event_Code|Ticker|事件中文</t>
         </is>
       </c>
       <c r="BJ5" s="4" t="inlineStr"/>
